--- a/construction_template/data/templates_blank/self_inspection.xlsx
+++ b/construction_template/data/templates_blank/self_inspection.xlsx
@@ -297,7 +297,7 @@
     <t xml:space="preserve">QR</t>
   </si>
   <si>
-    <t xml:space="preserve">任泰技術顧問有限公司</t>
+    <t xml:space="preserve"/>
   </si>
   <si>
     <t xml:space="preserve">              測量放樣施工抽查紀錄表</t>
@@ -328,7 +328,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">工程名稱</t>
+      <t xml:space="preserve">工程名稱:</t>
     </r>
     <r>
       <rPr>
@@ -338,7 +338,7 @@
         <family val="4"/>
         <charset val="136"/>
       </rPr>
-      <t xml:space="preserve">:</t>
+      <t xml:space="preserve"/>
     </r>
     <r>
       <rPr>
@@ -347,7 +347,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">延平河濱公園</t>
+      <t xml:space="preserve"/>
     </r>
     <r>
       <rPr>
@@ -357,7 +357,7 @@
         <family val="4"/>
         <charset val="136"/>
       </rPr>
-      <t xml:space="preserve">(</t>
+      <t xml:space="preserve"/>
     </r>
     <r>
       <rPr>
@@ -366,7 +366,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">大稻埕碼頭至忠孝橋下</t>
+      <t xml:space="preserve"/>
     </r>
     <r>
       <rPr>
@@ -376,7 +376,7 @@
         <family val="4"/>
         <charset val="136"/>
       </rPr>
-      <t xml:space="preserve">)</t>
+      <t xml:space="preserve"/>
     </r>
     <r>
       <rPr>
@@ -385,7 +385,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">區域改善工程</t>
+      <t xml:space="preserve"/>
     </r>
   </si>
   <si>
@@ -1103,7 +1103,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">工程名稱</t>
+      <t xml:space="preserve">工程名稱:</t>
     </r>
     <r>
       <rPr>
@@ -1112,7 +1112,7 @@
         <family val="4"/>
         <charset val="136"/>
       </rPr>
-      <t xml:space="preserve">:</t>
+      <t xml:space="preserve"/>
     </r>
     <r>
       <rPr>
@@ -1120,7 +1120,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">延平河濱公園</t>
+      <t xml:space="preserve"/>
     </r>
     <r>
       <rPr>
@@ -1129,7 +1129,7 @@
         <family val="4"/>
         <charset val="136"/>
       </rPr>
-      <t xml:space="preserve">(</t>
+      <t xml:space="preserve"/>
     </r>
     <r>
       <rPr>
@@ -1137,7 +1137,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">大稻埕碼頭至忠孝橋下</t>
+      <t xml:space="preserve"/>
     </r>
     <r>
       <rPr>
@@ -1146,7 +1146,7 @@
         <family val="4"/>
         <charset val="136"/>
       </rPr>
-      <t xml:space="preserve">)</t>
+      <t xml:space="preserve"/>
     </r>
     <r>
       <rPr>
@@ -1154,7 +1154,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">區域改善工程</t>
+      <t xml:space="preserve"/>
     </r>
   </si>
   <si>
@@ -2330,7 +2330,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">拌合廠（</t>
+      <t xml:space="preserve"/>
     </r>
     <r>
       <rPr>
@@ -2339,7 +2339,7 @@
         <family val="4"/>
         <charset val="136"/>
       </rPr>
-      <t xml:space="preserve">1.</t>
+      <t xml:space="preserve"/>
     </r>
     <r>
       <rPr>
@@ -2347,7 +2347,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">台灣區預拌混凝土工業同業公會會員證書、</t>
+      <t xml:space="preserve"/>
     </r>
     <r>
       <rPr>
@@ -2356,7 +2356,7 @@
         <family val="4"/>
         <charset val="136"/>
       </rPr>
-      <t xml:space="preserve">2.</t>
+      <t xml:space="preserve"/>
     </r>
     <r>
       <rPr>
@@ -2364,7 +2364,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">經濟部工廠登記證、</t>
+      <t xml:space="preserve"/>
     </r>
     <r>
       <rPr>
@@ -2373,7 +2373,7 @@
         <family val="4"/>
         <charset val="136"/>
       </rPr>
-      <t xml:space="preserve">3.</t>
+      <t xml:space="preserve"/>
     </r>
     <r>
       <rPr>
@@ -2381,7 +2381,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">當地環保許可證、</t>
+      <t xml:space="preserve"/>
     </r>
     <r>
       <rPr>
@@ -2390,7 +2390,7 @@
         <family val="4"/>
         <charset val="136"/>
       </rPr>
-      <t xml:space="preserve">4.</t>
+      <t xml:space="preserve"/>
     </r>
     <r>
       <rPr>
@@ -2398,7 +2398,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">預拌混凝土配合比設計表、</t>
+      <t xml:space="preserve"/>
     </r>
     <r>
       <rPr>
@@ -2407,7 +2407,7 @@
         <family val="4"/>
         <charset val="136"/>
       </rPr>
-      <t xml:space="preserve">5.</t>
+      <t xml:space="preserve"/>
     </r>
     <r>
       <rPr>
@@ -2415,7 +2415,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">承攬廠商與預拌混凝土供料商之訂購單或合約副本或相關買賣證明）經本處於</t>
+      <t xml:space="preserve"/>
     </r>
     <r>
       <rPr>
@@ -2426,7 +2426,7 @@
         <family val="4"/>
         <charset val="136"/>
       </rPr>
-      <t xml:space="preserve">109</t>
+      <t xml:space="preserve"/>
     </r>
     <r>
       <rPr>
@@ -2435,7 +2435,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">年</t>
+      <t xml:space="preserve"/>
     </r>
     <r>
       <rPr>
@@ -2446,7 +2446,7 @@
         <family val="4"/>
         <charset val="136"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve"/>
     </r>
     <r>
       <rPr>
@@ -2455,7 +2455,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">月</t>
+      <t xml:space="preserve"/>
     </r>
     <r>
       <rPr>
@@ -2465,7 +2465,7 @@
         <family val="4"/>
         <charset val="136"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve"/>
     </r>
     <r>
       <rPr>
@@ -2474,7 +2474,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">日</t>
+      <t xml:space="preserve"/>
     </r>
     <r>
       <rPr>
@@ -2482,7 +2482,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">同意備查使用。</t>
+      <t xml:space="preserve"/>
     </r>
   </si>
   <si>
@@ -4409,7 +4409,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">臺北市政府工務局水利工程處</t>
+    <t xml:space="preserve"/>
   </si>
   <si>
     <t xml:space="preserve">              銑刨施工抽查紀錄表</t>
@@ -7690,7 +7690,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">工程名稱</t>
+      <t xml:space="preserve">工程名稱:</t>
     </r>
     <r>
       <rPr>
@@ -7700,7 +7700,7 @@
         <family val="4"/>
         <charset val="136"/>
       </rPr>
-      <t xml:space="preserve">:</t>
+      <t xml:space="preserve"/>
     </r>
     <r>
       <rPr>
@@ -7709,7 +7709,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">延平河濱公園</t>
+      <t xml:space="preserve"/>
     </r>
     <r>
       <rPr>
@@ -7719,7 +7719,7 @@
         <family val="4"/>
         <charset val="136"/>
       </rPr>
-      <t xml:space="preserve">(</t>
+      <t xml:space="preserve"/>
     </r>
     <r>
       <rPr>
@@ -7728,7 +7728,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">大稻埕碼頭至忠孝橋下</t>
+      <t xml:space="preserve"/>
     </r>
     <r>
       <rPr>
@@ -7738,7 +7738,7 @@
         <family val="4"/>
         <charset val="136"/>
       </rPr>
-      <t xml:space="preserve">)</t>
+      <t xml:space="preserve"/>
     </r>
     <r>
       <rPr>
@@ -7747,7 +7747,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">區域改善工程</t>
+      <t xml:space="preserve"/>
     </r>
   </si>
   <si>

--- a/construction_template/data/templates_blank/self_inspection.xlsx
+++ b/construction_template/data/templates_blank/self_inspection.xlsx
@@ -10884,7 +10884,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
@@ -11318,7 +11318,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
@@ -11440,7 +11440,7 @@
       <c r="E9" s="150"/>
     </row>
     <row r="10" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="36" t="n"/>
+      <c r="A10" s="36"/>
       <c r="B10" s="90" t="s">
         <v>89</v>
       </c>
@@ -11460,7 +11460,7 @@
       <c r="E11" s="152"/>
     </row>
     <row r="12" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="51" t="n"/>
+      <c r="A12" s="51"/>
       <c r="B12" s="108" t="s">
         <v>279</v>
       </c>
@@ -11469,7 +11469,7 @@
       <c r="E12" s="151"/>
     </row>
     <row r="13" customFormat="false" ht="32.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="51" t="n"/>
+      <c r="A13" s="51"/>
       <c r="B13" s="108" t="s">
         <v>280</v>
       </c>
@@ -11480,7 +11480,7 @@
       <c r="E13" s="151"/>
     </row>
     <row r="14" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="51" t="n"/>
+      <c r="A14" s="51"/>
       <c r="B14" s="108" t="s">
         <v>282</v>
       </c>
@@ -11489,7 +11489,7 @@
       <c r="E14" s="151"/>
     </row>
     <row r="15" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="51" t="n"/>
+      <c r="A15" s="51"/>
       <c r="B15" s="108" t="s">
         <v>283</v>
       </c>
@@ -11498,7 +11498,7 @@
       <c r="E15" s="151"/>
     </row>
     <row r="16" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="51" t="n"/>
+      <c r="A16" s="51"/>
       <c r="B16" s="53" t="s">
         <v>284</v>
       </c>
@@ -11507,7 +11507,7 @@
       <c r="E16" s="151"/>
     </row>
     <row r="17" customFormat="false" ht="48" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="51" t="n"/>
+      <c r="A17" s="51"/>
       <c r="B17" s="154" t="s">
         <v>285</v>
       </c>
@@ -11527,7 +11527,7 @@
       <c r="E18" s="155"/>
     </row>
     <row r="19" customFormat="false" ht="48" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="51" t="n"/>
+      <c r="A19" s="51"/>
       <c r="B19" s="89" t="s">
         <v>199</v>
       </c>
@@ -11549,7 +11549,7 @@
       <c r="E20" s="150"/>
     </row>
     <row r="21" customFormat="false" ht="47.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="51" t="n"/>
+      <c r="A21" s="51"/>
       <c r="B21" s="89" t="s">
         <v>289</v>
       </c>
@@ -11560,7 +11560,7 @@
       <c r="E21" s="151"/>
     </row>
     <row r="22" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="51" t="n"/>
+      <c r="A22" s="51"/>
       <c r="B22" s="89" t="s">
         <v>291</v>
       </c>
@@ -11569,7 +11569,7 @@
       <c r="E22" s="151"/>
     </row>
     <row r="23" customFormat="false" ht="31.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="51" t="n"/>
+      <c r="A23" s="51"/>
       <c r="B23" s="89" t="s">
         <v>292</v>
       </c>
@@ -11968,7 +11968,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
@@ -12090,7 +12090,7 @@
       <c r="E9" s="55"/>
     </row>
     <row r="10" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="36" t="n"/>
+      <c r="A10" s="36"/>
       <c r="B10" s="90" t="s">
         <v>89</v>
       </c>
@@ -12110,7 +12110,7 @@
       <c r="E11" s="31"/>
     </row>
     <row r="12" customFormat="false" ht="33.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="51" t="n"/>
+      <c r="A12" s="51"/>
       <c r="B12" s="57" t="s">
         <v>299</v>
       </c>
@@ -12121,7 +12121,7 @@
       <c r="E12" s="35"/>
     </row>
     <row r="13" customFormat="false" ht="33.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="51" t="n"/>
+      <c r="A13" s="51"/>
       <c r="B13" s="60" t="s">
         <v>301</v>
       </c>
@@ -12143,7 +12143,7 @@
       <c r="E14" s="71"/>
     </row>
     <row r="15" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="51" t="n"/>
+      <c r="A15" s="51"/>
       <c r="B15" s="162" t="s">
         <v>303</v>
       </c>
@@ -12154,7 +12154,7 @@
       <c r="E15" s="163"/>
     </row>
     <row r="16" customFormat="false" ht="33.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="51" t="n"/>
+      <c r="A16" s="51"/>
       <c r="B16" s="162" t="s">
         <v>305</v>
       </c>
@@ -12163,7 +12163,7 @@
       <c r="E16" s="163"/>
     </row>
     <row r="17" customFormat="false" ht="33.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="51" t="n"/>
+      <c r="A17" s="51"/>
       <c r="B17" s="162" t="s">
         <v>306</v>
       </c>
@@ -12172,7 +12172,7 @@
       <c r="E17" s="163"/>
     </row>
     <row r="18" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="51" t="n"/>
+      <c r="A18" s="51"/>
       <c r="B18" s="162" t="s">
         <v>307</v>
       </c>
@@ -12192,7 +12192,7 @@
       <c r="E19" s="71"/>
     </row>
     <row r="20" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="51" t="n"/>
+      <c r="A20" s="51"/>
       <c r="B20" s="57" t="s">
         <v>309</v>
       </c>
@@ -12201,7 +12201,7 @@
       <c r="E20" s="35"/>
     </row>
     <row r="21" customFormat="false" ht="33" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="51" t="n"/>
+      <c r="A21" s="51"/>
       <c r="B21" s="57" t="s">
         <v>310</v>
       </c>
@@ -12212,7 +12212,7 @@
       <c r="E21" s="35"/>
     </row>
     <row r="22" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="51" t="n"/>
+      <c r="A22" s="51"/>
       <c r="B22" s="164" t="s">
         <v>312</v>
       </c>
@@ -12234,7 +12234,7 @@
       <c r="E23" s="55"/>
     </row>
     <row r="24" customFormat="false" ht="33" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="51" t="n"/>
+      <c r="A24" s="51"/>
       <c r="B24" s="57" t="s">
         <v>316</v>
       </c>
@@ -12243,7 +12243,7 @@
       <c r="E24" s="35"/>
     </row>
     <row r="25" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="51" t="n"/>
+      <c r="A25" s="51"/>
       <c r="B25" s="57" t="s">
         <v>317</v>
       </c>
@@ -12254,7 +12254,7 @@
       <c r="E25" s="35"/>
     </row>
     <row r="26" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="51" t="n"/>
+      <c r="A26" s="51"/>
       <c r="B26" s="57" t="s">
         <v>319</v>
       </c>
@@ -12263,7 +12263,7 @@
       <c r="E26" s="35"/>
     </row>
     <row r="27" customFormat="false" ht="126.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="51" t="n"/>
+      <c r="A27" s="51"/>
       <c r="B27" s="57" t="s">
         <v>222</v>
       </c>
@@ -12666,7 +12666,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
@@ -12788,7 +12788,7 @@
       <c r="E9" s="55"/>
     </row>
     <row r="10" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="36" t="n"/>
+      <c r="A10" s="36"/>
       <c r="B10" s="90" t="s">
         <v>89</v>
       </c>
@@ -12810,7 +12810,7 @@
       <c r="E11" s="31"/>
     </row>
     <row r="12" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="51" t="n"/>
+      <c r="A12" s="51"/>
       <c r="B12" s="57" t="s">
         <v>99</v>
       </c>
@@ -12821,7 +12821,7 @@
       <c r="E12" s="35"/>
     </row>
     <row r="13" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="51" t="n"/>
+      <c r="A13" s="51"/>
       <c r="B13" s="89" t="s">
         <v>324</v>
       </c>
@@ -12832,7 +12832,7 @@
       <c r="E13" s="35"/>
     </row>
     <row r="14" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="51" t="n"/>
+      <c r="A14" s="51"/>
       <c r="B14" s="57" t="s">
         <v>326</v>
       </c>
@@ -12843,7 +12843,7 @@
       <c r="E14" s="35"/>
     </row>
     <row r="15" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="51" t="n"/>
+      <c r="A15" s="51"/>
       <c r="B15" s="89" t="s">
         <v>327</v>
       </c>
@@ -12854,7 +12854,7 @@
       <c r="E15" s="35"/>
     </row>
     <row r="16" customFormat="false" ht="33" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="51" t="n"/>
+      <c r="A16" s="51"/>
       <c r="B16" s="53" t="s">
         <v>329</v>
       </c>
@@ -12876,7 +12876,7 @@
       <c r="E17" s="71"/>
     </row>
     <row r="18" customFormat="false" ht="33" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="51" t="n"/>
+      <c r="A18" s="51"/>
       <c r="B18" s="57" t="s">
         <v>331</v>
       </c>
@@ -12887,7 +12887,7 @@
       <c r="E18" s="35"/>
     </row>
     <row r="19" customFormat="false" ht="33" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="51" t="n"/>
+      <c r="A19" s="51"/>
       <c r="B19" s="57" t="s">
         <v>332</v>
       </c>
@@ -12898,7 +12898,7 @@
       <c r="E19" s="35"/>
     </row>
     <row r="20" customFormat="false" ht="33" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="51" t="n"/>
+      <c r="A20" s="51"/>
       <c r="B20" s="57" t="s">
         <v>334</v>
       </c>
@@ -12909,7 +12909,7 @@
       <c r="E20" s="35"/>
     </row>
     <row r="21" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="51" t="n"/>
+      <c r="A21" s="51"/>
       <c r="B21" s="89" t="s">
         <v>335</v>
       </c>
@@ -12920,7 +12920,7 @@
       <c r="E21" s="35"/>
     </row>
     <row r="22" customFormat="false" ht="33" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="51" t="n"/>
+      <c r="A22" s="51"/>
       <c r="B22" s="57" t="s">
         <v>336</v>
       </c>
@@ -12931,7 +12931,7 @@
       <c r="E22" s="35"/>
     </row>
     <row r="23" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="51" t="n"/>
+      <c r="A23" s="51"/>
       <c r="B23" s="57" t="s">
         <v>338</v>
       </c>
@@ -12942,7 +12942,7 @@
       <c r="E23" s="35"/>
     </row>
     <row r="24" customFormat="false" ht="33" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="51" t="n"/>
+      <c r="A24" s="51"/>
       <c r="B24" s="57" t="s">
         <v>340</v>
       </c>
@@ -12953,7 +12953,7 @@
       <c r="E24" s="35"/>
     </row>
     <row r="25" customFormat="false" ht="33" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="51" t="n"/>
+      <c r="A25" s="51"/>
       <c r="B25" s="57" t="s">
         <v>342</v>
       </c>
@@ -12964,7 +12964,7 @@
       <c r="E25" s="35"/>
     </row>
     <row r="26" customFormat="false" ht="33" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="51" t="n"/>
+      <c r="A26" s="51"/>
       <c r="B26" s="57" t="s">
         <v>344</v>
       </c>
@@ -13364,7 +13364,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
@@ -13486,7 +13486,7 @@
       <c r="E9" s="177"/>
     </row>
     <row r="10" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="178" t="n"/>
+      <c r="A10" s="178"/>
       <c r="B10" s="179" t="s">
         <v>89</v>
       </c>
@@ -13508,7 +13508,7 @@
       <c r="E11" s="184"/>
     </row>
     <row r="12" customFormat="false" ht="28.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="185" t="n"/>
+      <c r="A12" s="185"/>
       <c r="B12" s="186" t="s">
         <v>99</v>
       </c>
@@ -13519,7 +13519,7 @@
       <c r="E12" s="182"/>
     </row>
     <row r="13" customFormat="false" ht="29.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="185" t="n"/>
+      <c r="A13" s="185"/>
       <c r="B13" s="179" t="s">
         <v>354</v>
       </c>
@@ -13530,7 +13530,7 @@
       <c r="E13" s="182"/>
     </row>
     <row r="14" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="185" t="n"/>
+      <c r="A14" s="185"/>
       <c r="B14" s="179" t="s">
         <v>356</v>
       </c>
@@ -13541,7 +13541,7 @@
       <c r="E14" s="182"/>
     </row>
     <row r="15" customFormat="false" ht="28.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="185" t="n"/>
+      <c r="A15" s="185"/>
       <c r="B15" s="188" t="s">
         <v>357</v>
       </c>
@@ -13563,7 +13563,7 @@
       <c r="E16" s="190"/>
     </row>
     <row r="17" customFormat="false" ht="28.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="185" t="n"/>
+      <c r="A17" s="185"/>
       <c r="B17" s="186" t="s">
         <v>331</v>
       </c>
@@ -13574,7 +13574,7 @@
       <c r="E17" s="182"/>
     </row>
     <row r="18" customFormat="false" ht="28.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="185" t="n"/>
+      <c r="A18" s="185"/>
       <c r="B18" s="186" t="s">
         <v>332</v>
       </c>
@@ -13585,7 +13585,7 @@
       <c r="E18" s="182"/>
     </row>
     <row r="19" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="185" t="n"/>
+      <c r="A19" s="185"/>
       <c r="B19" s="186" t="s">
         <v>336</v>
       </c>
@@ -13596,7 +13596,7 @@
       <c r="E19" s="182"/>
     </row>
     <row r="20" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="185" t="n"/>
+      <c r="A20" s="185"/>
       <c r="B20" s="186" t="s">
         <v>359</v>
       </c>
@@ -13607,7 +13607,7 @@
       <c r="E20" s="182"/>
     </row>
     <row r="21" customFormat="false" ht="28.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="185" t="n"/>
+      <c r="A21" s="185"/>
       <c r="B21" s="186" t="s">
         <v>360</v>
       </c>
@@ -13618,7 +13618,7 @@
       <c r="E21" s="182"/>
     </row>
     <row r="22" customFormat="false" ht="28.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="185" t="n"/>
+      <c r="A22" s="185"/>
       <c r="B22" s="186" t="s">
         <v>361</v>
       </c>
@@ -13629,7 +13629,7 @@
       <c r="E22" s="182"/>
     </row>
     <row r="23" customFormat="false" ht="28.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="185" t="n"/>
+      <c r="A23" s="185"/>
       <c r="B23" s="186" t="s">
         <v>344</v>
       </c>
@@ -14030,7 +14030,7 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
@@ -14152,7 +14152,7 @@
       <c r="E9" s="150"/>
     </row>
     <row r="10" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="36" t="n"/>
+      <c r="A10" s="36"/>
       <c r="B10" s="90" t="s">
         <v>89</v>
       </c>
@@ -14172,7 +14172,7 @@
       <c r="E11" s="152"/>
     </row>
     <row r="12" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="51" t="n"/>
+      <c r="A12" s="51"/>
       <c r="B12" s="89" t="s">
         <v>366</v>
       </c>
@@ -14192,7 +14192,7 @@
       <c r="E13" s="155"/>
     </row>
     <row r="14" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="51" t="n"/>
+      <c r="A14" s="51"/>
       <c r="B14" s="89" t="s">
         <v>368</v>
       </c>
@@ -14212,7 +14212,7 @@
       <c r="E15" s="150"/>
     </row>
     <row r="16" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="51" t="n"/>
+      <c r="A16" s="51"/>
       <c r="B16" s="89" t="s">
         <v>370</v>
       </c>
@@ -14221,7 +14221,7 @@
       <c r="E16" s="151"/>
     </row>
     <row r="17" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="51" t="n"/>
+      <c r="A17" s="51"/>
       <c r="B17" s="89" t="s">
         <v>371</v>
       </c>
@@ -14230,7 +14230,7 @@
       <c r="E17" s="151"/>
     </row>
     <row r="18" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="51" t="n"/>
+      <c r="A18" s="51"/>
       <c r="B18" s="89" t="s">
         <v>372</v>
       </c>
@@ -14241,7 +14241,7 @@
       <c r="E18" s="151"/>
     </row>
     <row r="19" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="51" t="n"/>
+      <c r="A19" s="51"/>
       <c r="B19" s="89" t="s">
         <v>374</v>
       </c>
@@ -14250,7 +14250,7 @@
       <c r="E19" s="151"/>
     </row>
     <row r="20" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="51" t="n"/>
+      <c r="A20" s="51"/>
       <c r="B20" s="89" t="s">
         <v>375</v>
       </c>
@@ -14259,7 +14259,7 @@
       <c r="E20" s="151"/>
     </row>
     <row r="21" customFormat="false" ht="31.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="51" t="n"/>
+      <c r="A21" s="51"/>
       <c r="B21" s="89" t="s">
         <v>376</v>
       </c>
@@ -14268,7 +14268,7 @@
       <c r="E21" s="151"/>
     </row>
     <row r="22" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="51" t="n"/>
+      <c r="A22" s="51"/>
       <c r="B22" s="89" t="s">
         <v>377</v>
       </c>
@@ -14277,7 +14277,7 @@
       <c r="E22" s="151"/>
     </row>
     <row r="23" customFormat="false" ht="31.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="51" t="n"/>
+      <c r="A23" s="51"/>
       <c r="B23" s="89" t="s">
         <v>378</v>
       </c>
@@ -14297,7 +14297,7 @@
       <c r="E24" s="150"/>
     </row>
     <row r="25" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="51" t="n"/>
+      <c r="A25" s="51"/>
       <c r="B25" s="89" t="s">
         <v>379</v>
       </c>
@@ -14306,7 +14306,7 @@
       <c r="E25" s="151"/>
     </row>
     <row r="26" customFormat="false" ht="44.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="51" t="n"/>
+      <c r="A26" s="51"/>
       <c r="B26" s="89" t="s">
         <v>380</v>
       </c>
@@ -14315,7 +14315,7 @@
       <c r="E26" s="151"/>
     </row>
     <row r="27" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="51" t="n"/>
+      <c r="A27" s="51"/>
       <c r="B27" s="89" t="s">
         <v>381</v>
       </c>
@@ -14715,7 +14715,7 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
@@ -14837,7 +14837,7 @@
       <c r="E9" s="55"/>
     </row>
     <row r="10" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="36" t="n"/>
+      <c r="A10" s="36"/>
       <c r="B10" s="90" t="s">
         <v>89</v>
       </c>
@@ -14857,7 +14857,7 @@
       <c r="E11" s="31"/>
     </row>
     <row r="12" customFormat="false" ht="28.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="51" t="n"/>
+      <c r="A12" s="51"/>
       <c r="B12" s="57" t="s">
         <v>384</v>
       </c>
@@ -14868,7 +14868,7 @@
       <c r="E12" s="35"/>
     </row>
     <row r="13" customFormat="false" ht="33.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="51" t="n"/>
+      <c r="A13" s="51"/>
       <c r="B13" s="60" t="s">
         <v>366</v>
       </c>
@@ -14888,7 +14888,7 @@
       <c r="E14" s="71"/>
     </row>
     <row r="15" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="51" t="n"/>
+      <c r="A15" s="51"/>
       <c r="B15" s="89" t="s">
         <v>386</v>
       </c>
@@ -14897,7 +14897,7 @@
       <c r="E15" s="35"/>
     </row>
     <row r="16" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="51" t="n"/>
+      <c r="A16" s="51"/>
       <c r="B16" s="57" t="s">
         <v>387</v>
       </c>
@@ -14917,7 +14917,7 @@
       <c r="E17" s="35"/>
     </row>
     <row r="18" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="51" t="n"/>
+      <c r="A18" s="51"/>
       <c r="B18" s="57" t="s">
         <v>388</v>
       </c>
@@ -14926,7 +14926,7 @@
       <c r="E18" s="35"/>
     </row>
     <row r="19" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="51" t="n"/>
+      <c r="A19" s="51"/>
       <c r="B19" s="57" t="s">
         <v>389</v>
       </c>
@@ -14935,7 +14935,7 @@
       <c r="E19" s="35"/>
     </row>
     <row r="20" customFormat="false" ht="33" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="51" t="n"/>
+      <c r="A20" s="51"/>
       <c r="B20" s="57" t="s">
         <v>390</v>
       </c>
@@ -14946,7 +14946,7 @@
       <c r="E20" s="35"/>
     </row>
     <row r="21" customFormat="false" ht="33" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="51" t="n"/>
+      <c r="A21" s="51"/>
       <c r="B21" s="57" t="s">
         <v>391</v>
       </c>
@@ -14955,7 +14955,7 @@
       <c r="E21" s="35"/>
     </row>
     <row r="22" customFormat="false" ht="33" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="51" t="n"/>
+      <c r="A22" s="51"/>
       <c r="B22" s="57" t="s">
         <v>392</v>
       </c>
@@ -14964,7 +14964,7 @@
       <c r="E22" s="35"/>
     </row>
     <row r="23" customFormat="false" ht="33" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="51" t="n"/>
+      <c r="A23" s="51"/>
       <c r="B23" s="57" t="s">
         <v>393</v>
       </c>
@@ -15362,7 +15362,7 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
@@ -15484,7 +15484,7 @@
       <c r="E9" s="55"/>
     </row>
     <row r="10" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="36" t="n"/>
+      <c r="A10" s="36"/>
       <c r="B10" s="90" t="s">
         <v>89</v>
       </c>
@@ -15504,7 +15504,7 @@
       <c r="E11" s="31"/>
     </row>
     <row r="12" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="51" t="n"/>
+      <c r="A12" s="51"/>
       <c r="B12" s="57" t="s">
         <v>396</v>
       </c>
@@ -15513,7 +15513,7 @@
       <c r="E12" s="35"/>
     </row>
     <row r="13" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="51" t="n"/>
+      <c r="A13" s="51"/>
       <c r="B13" s="60" t="s">
         <v>397</v>
       </c>
@@ -15533,7 +15533,7 @@
       <c r="E14" s="71"/>
     </row>
     <row r="15" customFormat="false" ht="33" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="51" t="n"/>
+      <c r="A15" s="51"/>
       <c r="B15" s="57" t="s">
         <v>398</v>
       </c>
@@ -15542,7 +15542,7 @@
       <c r="E15" s="35"/>
     </row>
     <row r="16" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="51" t="n"/>
+      <c r="A16" s="51"/>
       <c r="B16" s="57" t="s">
         <v>399</v>
       </c>
@@ -15551,7 +15551,7 @@
       <c r="E16" s="35"/>
     </row>
     <row r="17" customFormat="false" ht="33" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="51" t="n"/>
+      <c r="A17" s="51"/>
       <c r="B17" s="57" t="s">
         <v>400</v>
       </c>
@@ -15562,7 +15562,7 @@
       <c r="E17" s="35"/>
     </row>
     <row r="18" customFormat="false" ht="33" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="51" t="n"/>
+      <c r="A18" s="51"/>
       <c r="B18" s="57" t="s">
         <v>402</v>
       </c>
@@ -15573,7 +15573,7 @@
       <c r="E18" s="35"/>
     </row>
     <row r="19" customFormat="false" ht="33" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="51" t="n"/>
+      <c r="A19" s="51"/>
       <c r="B19" s="57" t="s">
         <v>404</v>
       </c>
@@ -15994,7 +15994,7 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
@@ -16116,7 +16116,7 @@
       <c r="E9" s="55"/>
     </row>
     <row r="10" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="36" t="n"/>
+      <c r="A10" s="36"/>
       <c r="B10" s="90" t="s">
         <v>89</v>
       </c>
@@ -16136,7 +16136,7 @@
       <c r="E11" s="31"/>
     </row>
     <row r="12" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="51" t="n"/>
+      <c r="A12" s="51"/>
       <c r="B12" s="57" t="s">
         <v>407</v>
       </c>
@@ -16147,7 +16147,7 @@
       <c r="E12" s="35"/>
     </row>
     <row r="13" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="51" t="n"/>
+      <c r="A13" s="51"/>
       <c r="B13" s="60" t="s">
         <v>409</v>
       </c>
@@ -16158,7 +16158,7 @@
       <c r="E13" s="35"/>
     </row>
     <row r="14" customFormat="false" ht="33.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="51" t="n"/>
+      <c r="A14" s="51"/>
       <c r="B14" s="57" t="s">
         <v>411</v>
       </c>
@@ -16180,7 +16180,7 @@
       <c r="E15" s="71"/>
     </row>
     <row r="16" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="51" t="n"/>
+      <c r="A16" s="51"/>
       <c r="B16" s="162" t="s">
         <v>413</v>
       </c>
@@ -16191,7 +16191,7 @@
       <c r="E16" s="163"/>
     </row>
     <row r="17" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="51" t="n"/>
+      <c r="A17" s="51"/>
       <c r="B17" s="162" t="s">
         <v>415</v>
       </c>
@@ -16213,7 +16213,7 @@
       <c r="E18" s="71"/>
     </row>
     <row r="19" customFormat="false" ht="32.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="51" t="n"/>
+      <c r="A19" s="51"/>
       <c r="B19" s="53" t="s">
         <v>418</v>
       </c>
@@ -16628,7 +16628,7 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
@@ -16750,7 +16750,7 @@
       <c r="E9" s="55"/>
     </row>
     <row r="10" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="36" t="n"/>
+      <c r="A10" s="36"/>
       <c r="B10" s="90" t="s">
         <v>89</v>
       </c>
@@ -16770,7 +16770,7 @@
       <c r="E11" s="31"/>
     </row>
     <row r="12" customFormat="false" ht="33.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="51" t="n"/>
+      <c r="A12" s="51"/>
       <c r="B12" s="57" t="s">
         <v>421</v>
       </c>
@@ -16792,7 +16792,7 @@
       <c r="E13" s="71"/>
     </row>
     <row r="14" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="51" t="n"/>
+      <c r="A14" s="51"/>
       <c r="B14" s="162" t="s">
         <v>423</v>
       </c>
@@ -16803,7 +16803,7 @@
       <c r="E14" s="163"/>
     </row>
     <row r="15" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="51" t="n"/>
+      <c r="A15" s="51"/>
       <c r="B15" s="162" t="s">
         <v>425</v>
       </c>
@@ -16814,7 +16814,7 @@
       <c r="E15" s="163"/>
     </row>
     <row r="16" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="51" t="n"/>
+      <c r="A16" s="51"/>
       <c r="B16" s="162" t="s">
         <v>427</v>
       </c>
@@ -16825,7 +16825,7 @@
       <c r="E16" s="163"/>
     </row>
     <row r="17" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="51" t="n"/>
+      <c r="A17" s="51"/>
       <c r="B17" s="162" t="s">
         <v>429</v>
       </c>
@@ -16836,7 +16836,7 @@
       <c r="E17" s="163"/>
     </row>
     <row r="18" customFormat="false" ht="33.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="51" t="n"/>
+      <c r="A18" s="51"/>
       <c r="B18" s="53" t="s">
         <v>431</v>
       </c>
@@ -16858,7 +16858,7 @@
       <c r="E19" s="71"/>
     </row>
     <row r="20" customFormat="false" ht="33.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="51" t="n"/>
+      <c r="A20" s="51"/>
       <c r="B20" s="162" t="s">
         <v>433</v>
       </c>
@@ -17273,7 +17273,7 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
@@ -17395,7 +17395,7 @@
       <c r="E9" s="55"/>
     </row>
     <row r="10" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="36" t="n"/>
+      <c r="A10" s="36"/>
       <c r="B10" s="90" t="s">
         <v>89</v>
       </c>
@@ -17417,7 +17417,7 @@
       <c r="E11" s="31"/>
     </row>
     <row r="12" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="51" t="n"/>
+      <c r="A12" s="51"/>
       <c r="B12" s="57" t="s">
         <v>437</v>
       </c>
@@ -17428,7 +17428,7 @@
       <c r="E12" s="35"/>
     </row>
     <row r="13" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="51" t="n"/>
+      <c r="A13" s="51"/>
       <c r="B13" s="60" t="s">
         <v>99</v>
       </c>
@@ -17439,7 +17439,7 @@
       <c r="E13" s="35"/>
     </row>
     <row r="14" customFormat="false" ht="33.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="51" t="n"/>
+      <c r="A14" s="51"/>
       <c r="B14" s="60" t="s">
         <v>440</v>
       </c>
@@ -17450,7 +17450,7 @@
       <c r="E14" s="35"/>
     </row>
     <row r="15" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="51" t="n"/>
+      <c r="A15" s="51"/>
       <c r="B15" s="60" t="s">
         <v>442</v>
       </c>
@@ -17461,7 +17461,7 @@
       <c r="E15" s="35"/>
     </row>
     <row r="16" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="51" t="n"/>
+      <c r="A16" s="51"/>
       <c r="B16" s="53" t="s">
         <v>444</v>
       </c>
@@ -17483,7 +17483,7 @@
       <c r="E17" s="71"/>
     </row>
     <row r="18" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="51" t="n"/>
+      <c r="A18" s="51"/>
       <c r="B18" s="57" t="s">
         <v>447</v>
       </c>
@@ -17494,7 +17494,7 @@
       <c r="E18" s="35"/>
     </row>
     <row r="19" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="51" t="n"/>
+      <c r="A19" s="51"/>
       <c r="B19" s="89" t="s">
         <v>449</v>
       </c>
@@ -17516,7 +17516,7 @@
       <c r="E20" s="55"/>
     </row>
     <row r="21" customFormat="false" ht="33" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="51" t="n"/>
+      <c r="A21" s="51"/>
       <c r="B21" s="57" t="s">
         <v>451</v>
       </c>
@@ -17527,7 +17527,7 @@
       <c r="E21" s="35"/>
     </row>
     <row r="22" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="51" t="n"/>
+      <c r="A22" s="51"/>
       <c r="B22" s="89" t="s">
         <v>452</v>
       </c>
@@ -17538,7 +17538,7 @@
       <c r="E22" s="35"/>
     </row>
     <row r="23" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="51" t="n"/>
+      <c r="A23" s="51"/>
       <c r="B23" s="89" t="s">
         <v>453</v>
       </c>
@@ -17946,7 +17946,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
@@ -18068,7 +18068,7 @@
       <c r="E9" s="31"/>
     </row>
     <row r="10" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="32" t="n"/>
+      <c r="A10" s="32"/>
       <c r="B10" s="33" t="s">
         <v>89</v>
       </c>
@@ -18090,7 +18090,7 @@
       <c r="E11" s="31"/>
     </row>
     <row r="12" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="36" t="n"/>
+      <c r="A12" s="36"/>
       <c r="B12" s="37" t="s">
         <v>93</v>
       </c>
@@ -18112,7 +18112,7 @@
       <c r="E13" s="31"/>
     </row>
     <row r="14" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="36" t="n"/>
+      <c r="A14" s="36"/>
       <c r="B14" s="37" t="s">
         <v>97</v>
       </c>
@@ -18123,7 +18123,7 @@
       <c r="E14" s="35"/>
     </row>
     <row r="15" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="39" t="n"/>
+      <c r="A15" s="39"/>
       <c r="B15" s="40" t="s">
         <v>99</v>
       </c>
@@ -18134,7 +18134,7 @@
       <c r="E15" s="35"/>
     </row>
     <row r="16" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="36" t="n"/>
+      <c r="A16" s="36"/>
       <c r="B16" s="37" t="s">
         <v>101</v>
       </c>
@@ -18156,7 +18156,7 @@
       <c r="E17" s="42"/>
     </row>
     <row r="18" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="36" t="n"/>
+      <c r="A18" s="36"/>
       <c r="B18" s="37" t="s">
         <v>105</v>
       </c>
@@ -18167,7 +18167,7 @@
       <c r="E18" s="35"/>
     </row>
     <row r="19" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="39" t="n"/>
+      <c r="A19" s="39"/>
       <c r="B19" s="37" t="s">
         <v>106</v>
       </c>
@@ -18178,7 +18178,7 @@
       <c r="E19" s="35"/>
     </row>
     <row r="20" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="36" t="n"/>
+      <c r="A20" s="36"/>
       <c r="B20" s="37" t="s">
         <v>107</v>
       </c>
@@ -18593,7 +18593,7 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
@@ -18715,7 +18715,7 @@
       <c r="E9" s="55"/>
     </row>
     <row r="10" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="36" t="n"/>
+      <c r="A10" s="36"/>
       <c r="B10" s="90" t="s">
         <v>89</v>
       </c>
@@ -18735,7 +18735,7 @@
       <c r="E11" s="31"/>
     </row>
     <row r="12" customFormat="false" ht="42.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="51" t="n"/>
+      <c r="A12" s="51"/>
       <c r="B12" s="57" t="s">
         <v>456</v>
       </c>
@@ -18746,7 +18746,7 @@
       <c r="E12" s="35"/>
     </row>
     <row r="13" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="51" t="n"/>
+      <c r="A13" s="51"/>
       <c r="B13" s="60" t="s">
         <v>458</v>
       </c>
@@ -18755,7 +18755,7 @@
       <c r="E13" s="35"/>
     </row>
     <row r="14" customFormat="false" ht="57" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="51" t="n"/>
+      <c r="A14" s="51"/>
       <c r="B14" s="57" t="s">
         <v>459</v>
       </c>
@@ -18777,7 +18777,7 @@
       <c r="E15" s="71"/>
     </row>
     <row r="16" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="51" t="n"/>
+      <c r="A16" s="51"/>
       <c r="B16" s="57" t="s">
         <v>461</v>
       </c>
@@ -18786,7 +18786,7 @@
       <c r="E16" s="35"/>
     </row>
     <row r="17" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="51" t="n"/>
+      <c r="A17" s="51"/>
       <c r="B17" s="57" t="s">
         <v>99</v>
       </c>
@@ -18808,7 +18808,7 @@
       <c r="E18" s="55"/>
     </row>
     <row r="19" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="51" t="n"/>
+      <c r="A19" s="51"/>
       <c r="B19" s="89" t="s">
         <v>463</v>
       </c>
@@ -18817,7 +18817,7 @@
       <c r="E19" s="35"/>
     </row>
     <row r="20" customFormat="false" ht="31.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="51" t="n"/>
+      <c r="A20" s="51"/>
       <c r="B20" s="89" t="s">
         <v>464</v>
       </c>
@@ -18828,7 +18828,7 @@
       <c r="E20" s="35"/>
     </row>
     <row r="21" customFormat="false" ht="28.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="51" t="n"/>
+      <c r="A21" s="51"/>
       <c r="B21" s="89" t="s">
         <v>466</v>
       </c>
@@ -18839,7 +18839,7 @@
       <c r="E21" s="35"/>
     </row>
     <row r="22" customFormat="false" ht="28.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="51" t="n"/>
+      <c r="A22" s="51"/>
       <c r="B22" s="89" t="s">
         <v>468</v>
       </c>
@@ -18850,7 +18850,7 @@
       <c r="E22" s="35"/>
     </row>
     <row r="23" customFormat="false" ht="28.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="51" t="n"/>
+      <c r="A23" s="51"/>
       <c r="B23" s="89" t="s">
         <v>470</v>
       </c>
@@ -18861,7 +18861,7 @@
       <c r="E23" s="35"/>
     </row>
     <row r="24" customFormat="false" ht="22.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="51" t="n"/>
+      <c r="A24" s="51"/>
       <c r="B24" s="89" t="s">
         <v>472</v>
       </c>
@@ -18872,7 +18872,7 @@
       <c r="E24" s="35"/>
     </row>
     <row r="25" customFormat="false" ht="31.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="51" t="n"/>
+      <c r="A25" s="51"/>
       <c r="B25" s="89" t="s">
         <v>474</v>
       </c>
@@ -19273,7 +19273,7 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
@@ -19395,7 +19395,7 @@
       <c r="E9" s="55"/>
     </row>
     <row r="10" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="36" t="n"/>
+      <c r="A10" s="36"/>
       <c r="B10" s="90" t="s">
         <v>89</v>
       </c>
@@ -19415,7 +19415,7 @@
       <c r="E11" s="31"/>
     </row>
     <row r="12" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="51" t="n"/>
+      <c r="A12" s="51"/>
       <c r="B12" s="89" t="s">
         <v>478</v>
       </c>
@@ -19426,7 +19426,7 @@
       <c r="E12" s="35"/>
     </row>
     <row r="13" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="51" t="n"/>
+      <c r="A13" s="51"/>
       <c r="B13" s="60" t="s">
         <v>480</v>
       </c>
@@ -19435,7 +19435,7 @@
       <c r="E13" s="35"/>
     </row>
     <row r="14" customFormat="false" ht="33.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="51" t="n"/>
+      <c r="A14" s="51"/>
       <c r="B14" s="60" t="s">
         <v>481</v>
       </c>
@@ -19455,7 +19455,7 @@
       <c r="E15" s="71"/>
     </row>
     <row r="16" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="51" t="n"/>
+      <c r="A16" s="51"/>
       <c r="B16" s="89" t="s">
         <v>483</v>
       </c>
@@ -19464,7 +19464,7 @@
       <c r="E16" s="35"/>
     </row>
     <row r="17" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="51" t="n"/>
+      <c r="A17" s="51"/>
       <c r="B17" s="57" t="s">
         <v>484</v>
       </c>
@@ -19473,7 +19473,7 @@
       <c r="E17" s="35"/>
     </row>
     <row r="18" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="51" t="n"/>
+      <c r="A18" s="51"/>
       <c r="B18" s="57" t="s">
         <v>485</v>
       </c>
@@ -19482,7 +19482,7 @@
       <c r="E18" s="35"/>
     </row>
     <row r="19" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="51" t="n"/>
+      <c r="A19" s="51"/>
       <c r="B19" s="57" t="s">
         <v>486</v>
       </c>
@@ -19491,7 +19491,7 @@
       <c r="E19" s="35"/>
     </row>
     <row r="20" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="51" t="n"/>
+      <c r="A20" s="51"/>
       <c r="B20" s="57" t="s">
         <v>487</v>
       </c>
@@ -19513,7 +19513,7 @@
       <c r="E21" s="55"/>
     </row>
     <row r="22" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="51" t="n"/>
+      <c r="A22" s="51"/>
       <c r="B22" s="53" t="s">
         <v>490</v>
       </c>
@@ -19522,7 +19522,7 @@
       <c r="E22" s="203"/>
     </row>
     <row r="23" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="51" t="n"/>
+      <c r="A23" s="51"/>
       <c r="B23" s="53" t="s">
         <v>491</v>
       </c>
@@ -19533,7 +19533,7 @@
       <c r="E23" s="203"/>
     </row>
     <row r="24" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="51" t="n"/>
+      <c r="A24" s="51"/>
       <c r="B24" s="108" t="s">
         <v>493</v>
       </c>
@@ -19553,7 +19553,7 @@
       <c r="E25" s="55"/>
     </row>
     <row r="26" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="51" t="n"/>
+      <c r="A26" s="51"/>
       <c r="B26" s="53" t="s">
         <v>463</v>
       </c>
@@ -19562,7 +19562,7 @@
       <c r="E26" s="203"/>
     </row>
     <row r="27" customFormat="false" ht="33" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="51" t="n"/>
+      <c r="A27" s="51"/>
       <c r="B27" s="53" t="s">
         <v>464</v>
       </c>
@@ -19573,7 +19573,7 @@
       <c r="E27" s="203"/>
     </row>
     <row r="28" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="51" t="n"/>
+      <c r="A28" s="51"/>
       <c r="B28" s="57" t="s">
         <v>496</v>
       </c>
@@ -19584,7 +19584,7 @@
       <c r="E28" s="35"/>
     </row>
     <row r="29" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="51" t="n"/>
+      <c r="A29" s="51"/>
       <c r="B29" s="57" t="s">
         <v>498</v>
       </c>
@@ -19990,7 +19990,7 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
@@ -20112,7 +20112,7 @@
       <c r="E9" s="55"/>
     </row>
     <row r="10" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="36" t="n"/>
+      <c r="A10" s="36"/>
       <c r="B10" s="90" t="s">
         <v>89</v>
       </c>
@@ -20132,7 +20132,7 @@
       <c r="E11" s="31"/>
     </row>
     <row r="12" customFormat="false" ht="47.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="51" t="n"/>
+      <c r="A12" s="51"/>
       <c r="B12" s="89" t="s">
         <v>501</v>
       </c>
@@ -20143,7 +20143,7 @@
       <c r="E12" s="35"/>
     </row>
     <row r="13" customFormat="false" ht="32.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="51" t="n"/>
+      <c r="A13" s="51"/>
       <c r="B13" s="90" t="s">
         <v>503</v>
       </c>
@@ -20154,7 +20154,7 @@
       <c r="E13" s="35"/>
     </row>
     <row r="14" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="51" t="n"/>
+      <c r="A14" s="51"/>
       <c r="B14" s="90" t="s">
         <v>505</v>
       </c>
@@ -20165,7 +20165,7 @@
       <c r="E14" s="35"/>
     </row>
     <row r="15" customFormat="false" ht="31.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="51" t="n"/>
+      <c r="A15" s="51"/>
       <c r="B15" s="108" t="s">
         <v>506</v>
       </c>
@@ -20187,7 +20187,7 @@
       <c r="E16" s="71"/>
     </row>
     <row r="17" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="51" t="n"/>
+      <c r="A17" s="51"/>
       <c r="B17" s="89" t="s">
         <v>508</v>
       </c>
@@ -20198,7 +20198,7 @@
       <c r="E17" s="35"/>
     </row>
     <row r="18" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="51" t="n"/>
+      <c r="A18" s="51"/>
       <c r="B18" s="89" t="s">
         <v>510</v>
       </c>
@@ -20209,7 +20209,7 @@
       <c r="E18" s="35"/>
     </row>
     <row r="19" customFormat="false" ht="49.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="51" t="n"/>
+      <c r="A19" s="51"/>
       <c r="B19" s="89" t="s">
         <v>512</v>
       </c>
@@ -20220,7 +20220,7 @@
       <c r="E19" s="35"/>
     </row>
     <row r="20" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="51" t="n"/>
+      <c r="A20" s="51"/>
       <c r="B20" s="89" t="s">
         <v>514</v>
       </c>
@@ -20231,7 +20231,7 @@
       <c r="E20" s="35"/>
     </row>
     <row r="21" customFormat="false" ht="31.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="51" t="n"/>
+      <c r="A21" s="51"/>
       <c r="B21" s="89" t="s">
         <v>516</v>
       </c>
@@ -20242,7 +20242,7 @@
       <c r="E21" s="35"/>
     </row>
     <row r="22" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="51" t="n"/>
+      <c r="A22" s="51"/>
       <c r="B22" s="89" t="s">
         <v>518</v>
       </c>
@@ -20253,7 +20253,7 @@
       <c r="E22" s="35"/>
     </row>
     <row r="23" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="51" t="n"/>
+      <c r="A23" s="51"/>
       <c r="B23" s="89" t="s">
         <v>520</v>
       </c>
@@ -20275,7 +20275,7 @@
       <c r="E24" s="205"/>
     </row>
     <row r="25" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="51" t="n"/>
+      <c r="A25" s="51"/>
       <c r="B25" s="89" t="s">
         <v>521</v>
       </c>
@@ -20286,7 +20286,7 @@
       <c r="E25" s="35"/>
     </row>
     <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="51" t="n"/>
+      <c r="A26" s="51"/>
       <c r="B26" s="89" t="s">
         <v>523</v>
       </c>
@@ -20687,7 +20687,7 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
@@ -20809,7 +20809,7 @@
       <c r="E9" s="55"/>
     </row>
     <row r="10" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="36" t="n"/>
+      <c r="A10" s="36"/>
       <c r="B10" s="60" t="s">
         <v>89</v>
       </c>
@@ -20829,7 +20829,7 @@
       <c r="E11" s="31"/>
     </row>
     <row r="12" customFormat="false" ht="33" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="51" t="n"/>
+      <c r="A12" s="51"/>
       <c r="B12" s="57" t="s">
         <v>366</v>
       </c>
@@ -20851,7 +20851,7 @@
       <c r="E13" s="71"/>
     </row>
     <row r="14" customFormat="false" ht="33" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="51" t="n"/>
+      <c r="A14" s="51"/>
       <c r="B14" s="53" t="s">
         <v>528</v>
       </c>
@@ -20862,7 +20862,7 @@
       <c r="E14" s="162"/>
     </row>
     <row r="15" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="51" t="n"/>
+      <c r="A15" s="51"/>
       <c r="B15" s="53" t="s">
         <v>530</v>
       </c>
@@ -20873,7 +20873,7 @@
       <c r="E15" s="162"/>
     </row>
     <row r="16" customFormat="false" ht="33.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="51" t="n"/>
+      <c r="A16" s="51"/>
       <c r="B16" s="162" t="s">
         <v>532</v>
       </c>
@@ -20884,7 +20884,7 @@
       <c r="E16" s="162"/>
     </row>
     <row r="17" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="51" t="n"/>
+      <c r="A17" s="51"/>
       <c r="B17" s="57" t="s">
         <v>533</v>
       </c>
@@ -20895,7 +20895,7 @@
       <c r="E17" s="35"/>
     </row>
     <row r="18" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="51" t="n"/>
+      <c r="A18" s="51"/>
       <c r="B18" s="57" t="s">
         <v>535</v>
       </c>
@@ -20906,7 +20906,7 @@
       <c r="E18" s="35"/>
     </row>
     <row r="19" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="51" t="n"/>
+      <c r="A19" s="51"/>
       <c r="B19" s="57" t="s">
         <v>537</v>
       </c>
@@ -20928,7 +20928,7 @@
       <c r="E20" s="109"/>
     </row>
     <row r="21" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="51" t="n"/>
+      <c r="A21" s="51"/>
       <c r="B21" s="57" t="s">
         <v>539</v>
       </c>
@@ -21329,7 +21329,7 @@
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
@@ -21503,7 +21503,7 @@
       <c r="K9" s="220"/>
     </row>
     <row r="10" customFormat="false" ht="23.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="233" t="n"/>
+      <c r="A10" s="233"/>
       <c r="B10" s="234" t="s">
         <v>89</v>
       </c>
@@ -21537,7 +21537,7 @@
       <c r="K11" s="226"/>
     </row>
     <row r="12" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="233" t="n"/>
+      <c r="A12" s="233"/>
       <c r="B12" s="234" t="s">
         <v>550</v>
       </c>
@@ -21554,7 +21554,7 @@
       <c r="K12" s="236"/>
     </row>
     <row r="13" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="233" t="n"/>
+      <c r="A13" s="233"/>
       <c r="B13" s="234" t="s">
         <v>552</v>
       </c>
@@ -21571,7 +21571,7 @@
       <c r="K13" s="226"/>
     </row>
     <row r="14" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="233" t="n"/>
+      <c r="A14" s="233"/>
       <c r="B14" s="234" t="s">
         <v>554</v>
       </c>
@@ -21588,7 +21588,7 @@
       <c r="K14" s="226"/>
     </row>
     <row r="15" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="233" t="n"/>
+      <c r="A15" s="233"/>
       <c r="B15" s="234" t="s">
         <v>556</v>
       </c>
@@ -21959,7 +21959,7 @@
 </file>
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
@@ -22145,7 +22145,7 @@
       <c r="K10" s="236"/>
     </row>
     <row r="11" customFormat="false" ht="33" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="251" t="n"/>
+      <c r="A11" s="251"/>
       <c r="B11" s="272" t="s">
         <v>89</v>
       </c>
@@ -22177,7 +22177,7 @@
       <c r="K12" s="272"/>
     </row>
     <row r="13" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="251" t="n"/>
+      <c r="A13" s="251"/>
       <c r="B13" s="272" t="str">
         <f aca="false">[1]工作表2!B13</f>
         <v>種類</v>
@@ -22193,7 +22193,7 @@
       <c r="K13" s="251"/>
     </row>
     <row r="14" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="251" t="n"/>
+      <c r="A14" s="251"/>
       <c r="B14" s="272" t="str">
         <f aca="false">[1]工作表2!B14</f>
         <v>規格</v>
@@ -22211,7 +22211,7 @@
       <c r="K14" s="251"/>
     </row>
     <row r="15" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="251" t="n"/>
+      <c r="A15" s="251"/>
       <c r="B15" s="274" t="str">
         <f aca="false">[1]工作表2!B15</f>
         <v>外觀</v>
@@ -22242,7 +22242,7 @@
       <c r="K16" s="251"/>
     </row>
     <row r="17" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="251" t="n"/>
+      <c r="A17" s="251"/>
       <c r="B17" s="272" t="str">
         <f aca="false">[1]工作表2!B16</f>
         <v>相關文件</v>
@@ -22663,7 +22663,7 @@
 </file>
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
@@ -22785,7 +22785,7 @@
       <c r="E9" s="286"/>
     </row>
     <row r="10" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="130" t="n"/>
+      <c r="A10" s="130"/>
       <c r="B10" s="287" t="s">
         <v>89</v>
       </c>
@@ -22807,7 +22807,7 @@
       <c r="E11" s="288"/>
     </row>
     <row r="12" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="138" t="n"/>
+      <c r="A12" s="138"/>
       <c r="B12" s="289" t="s">
         <v>575</v>
       </c>
@@ -22818,7 +22818,7 @@
       <c r="E12" s="133"/>
     </row>
     <row r="13" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="138" t="n"/>
+      <c r="A13" s="138"/>
       <c r="B13" s="289" t="s">
         <v>576</v>
       </c>
@@ -22840,7 +22840,7 @@
       <c r="E14" s="286"/>
     </row>
     <row r="15" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="138" t="n"/>
+      <c r="A15" s="138"/>
       <c r="B15" s="289" t="s">
         <v>578</v>
       </c>
@@ -22851,7 +22851,7 @@
       <c r="E15" s="133"/>
     </row>
     <row r="16" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="138" t="n"/>
+      <c r="A16" s="138"/>
       <c r="B16" s="289" t="s">
         <v>580</v>
       </c>
@@ -22862,7 +22862,7 @@
       <c r="E16" s="133"/>
     </row>
     <row r="17" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="138" t="n"/>
+      <c r="A17" s="138"/>
       <c r="B17" s="289" t="s">
         <v>582</v>
       </c>
@@ -22873,7 +22873,7 @@
       <c r="E17" s="133"/>
     </row>
     <row r="18" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="138" t="n"/>
+      <c r="A18" s="138"/>
       <c r="B18" s="289" t="s">
         <v>584</v>
       </c>
@@ -22884,7 +22884,7 @@
       <c r="E18" s="133"/>
     </row>
     <row r="19" customFormat="false" ht="31.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="138" t="n"/>
+      <c r="A19" s="138"/>
       <c r="B19" s="289" t="s">
         <v>586</v>
       </c>
@@ -22895,7 +22895,7 @@
       <c r="E19" s="133"/>
     </row>
     <row r="20" customFormat="false" ht="32.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="138" t="n"/>
+      <c r="A20" s="138"/>
       <c r="B20" s="289" t="s">
         <v>588</v>
       </c>
@@ -22906,7 +22906,7 @@
       <c r="E20" s="133"/>
     </row>
     <row r="21" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="138" t="n"/>
+      <c r="A21" s="138"/>
       <c r="B21" s="289" t="s">
         <v>590</v>
       </c>
@@ -22928,7 +22928,7 @@
       <c r="E22" s="286"/>
     </row>
     <row r="23" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="138" t="n"/>
+      <c r="A23" s="138"/>
       <c r="B23" s="289" t="s">
         <v>592</v>
       </c>
@@ -23329,7 +23329,7 @@
 </file>
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
@@ -23451,7 +23451,7 @@
       <c r="E9" s="125"/>
     </row>
     <row r="10" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="130" t="n"/>
+      <c r="A10" s="130"/>
       <c r="B10" s="287" t="s">
         <v>89</v>
       </c>
@@ -23471,7 +23471,7 @@
       <c r="E11" s="131"/>
     </row>
     <row r="12" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="138" t="n"/>
+      <c r="A12" s="138"/>
       <c r="B12" s="289" t="s">
         <v>602</v>
       </c>
@@ -23482,7 +23482,7 @@
       <c r="E12" s="133"/>
     </row>
     <row r="13" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="138" t="n"/>
+      <c r="A13" s="138"/>
       <c r="B13" s="289" t="s">
         <v>604</v>
       </c>
@@ -23493,7 +23493,7 @@
       <c r="E13" s="133"/>
     </row>
     <row r="14" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="138" t="n"/>
+      <c r="A14" s="138"/>
       <c r="B14" s="289" t="s">
         <v>606</v>
       </c>
@@ -23504,7 +23504,7 @@
       <c r="E14" s="133"/>
     </row>
     <row r="15" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="138" t="n"/>
+      <c r="A15" s="138"/>
       <c r="B15" s="289" t="s">
         <v>608</v>
       </c>
@@ -23526,7 +23526,7 @@
       <c r="E16" s="302"/>
     </row>
     <row r="17" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="138" t="n"/>
+      <c r="A17" s="138"/>
       <c r="B17" s="289" t="s">
         <v>610</v>
       </c>
@@ -23537,7 +23537,7 @@
       <c r="E17" s="133"/>
     </row>
     <row r="18" customFormat="false" ht="31.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="138" t="n"/>
+      <c r="A18" s="138"/>
       <c r="B18" s="289" t="s">
         <v>611</v>
       </c>
@@ -23548,7 +23548,7 @@
       <c r="E18" s="133"/>
     </row>
     <row r="19" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="138" t="n"/>
+      <c r="A19" s="138"/>
       <c r="B19" s="289" t="s">
         <v>612</v>
       </c>
@@ -23948,7 +23948,7 @@
 </file>
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
@@ -24070,7 +24070,7 @@
       <c r="E9" s="286"/>
     </row>
     <row r="10" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="303" t="n"/>
+      <c r="A10" s="303"/>
       <c r="B10" s="289" t="s">
         <v>89</v>
       </c>
@@ -24092,7 +24092,7 @@
       <c r="E11" s="307"/>
     </row>
     <row r="12" customFormat="false" ht="33.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="138" t="n"/>
+      <c r="A12" s="138"/>
       <c r="B12" s="289" t="s">
         <v>615</v>
       </c>
@@ -24103,7 +24103,7 @@
       <c r="E12" s="306"/>
     </row>
     <row r="13" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="138" t="n"/>
+      <c r="A13" s="138"/>
       <c r="B13" s="289" t="s">
         <v>617</v>
       </c>
@@ -24114,7 +24114,7 @@
       <c r="E13" s="306"/>
     </row>
     <row r="14" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="138" t="n"/>
+      <c r="A14" s="138"/>
       <c r="B14" s="289" t="s">
         <v>619</v>
       </c>
@@ -24136,7 +24136,7 @@
       <c r="E15" s="286"/>
     </row>
     <row r="16" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="138" t="n"/>
+      <c r="A16" s="138"/>
       <c r="B16" s="289" t="s">
         <v>621</v>
       </c>
@@ -24147,7 +24147,7 @@
       <c r="E16" s="306"/>
     </row>
     <row r="17" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="138" t="n"/>
+      <c r="A17" s="138"/>
       <c r="B17" s="289" t="s">
         <v>623</v>
       </c>
@@ -24158,7 +24158,7 @@
       <c r="E17" s="306"/>
     </row>
     <row r="18" customFormat="false" ht="33.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="138" t="n"/>
+      <c r="A18" s="138"/>
       <c r="B18" s="289" t="s">
         <v>624</v>
       </c>
@@ -24180,7 +24180,7 @@
       <c r="E19" s="286"/>
     </row>
     <row r="20" customFormat="false" ht="33.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="138" t="n"/>
+      <c r="A20" s="138"/>
       <c r="B20" s="289" t="s">
         <v>625</v>
       </c>
@@ -24191,7 +24191,7 @@
       <c r="E20" s="306"/>
     </row>
     <row r="21" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="138" t="n"/>
+      <c r="A21" s="138"/>
       <c r="B21" s="289" t="s">
         <v>627</v>
       </c>
@@ -24202,7 +24202,7 @@
       <c r="E21" s="306"/>
     </row>
     <row r="22" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="138" t="n"/>
+      <c r="A22" s="138"/>
       <c r="B22" s="289" t="s">
         <v>629</v>
       </c>
@@ -24603,7 +24603,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
@@ -24725,7 +24725,7 @@
       <c r="E9" s="31"/>
     </row>
     <row r="10" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="51" t="n"/>
+      <c r="A10" s="51"/>
       <c r="B10" s="52" t="s">
         <v>89</v>
       </c>
@@ -24747,7 +24747,7 @@
       <c r="E11" s="31"/>
     </row>
     <row r="12" customFormat="false" ht="33" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="51" t="n"/>
+      <c r="A12" s="51"/>
       <c r="B12" s="53" t="s">
         <v>123</v>
       </c>
@@ -24769,7 +24769,7 @@
       <c r="E13" s="55"/>
     </row>
     <row r="14" customFormat="false" ht="28.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="51" t="n"/>
+      <c r="A14" s="51"/>
       <c r="B14" s="52" t="s">
         <v>125</v>
       </c>
@@ -24780,7 +24780,7 @@
       <c r="E14" s="35"/>
     </row>
     <row r="15" customFormat="false" ht="28.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="51" t="n"/>
+      <c r="A15" s="51"/>
       <c r="B15" s="37" t="s">
         <v>127</v>
       </c>
@@ -24791,7 +24791,7 @@
       <c r="E15" s="35"/>
     </row>
     <row r="16" s="59" customFormat="true" ht="33" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="51" t="n"/>
+      <c r="A16" s="51"/>
       <c r="B16" s="57" t="s">
         <v>129</v>
       </c>
@@ -24802,7 +24802,7 @@
       <c r="E16" s="58"/>
     </row>
     <row r="17" customFormat="false" ht="49.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="51" t="n"/>
+      <c r="A17" s="51"/>
       <c r="B17" s="57" t="s">
         <v>131</v>
       </c>
@@ -24813,7 +24813,7 @@
       <c r="E17" s="35"/>
     </row>
     <row r="18" customFormat="false" ht="33" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="51" t="n"/>
+      <c r="A18" s="51"/>
       <c r="B18" s="57" t="s">
         <v>133</v>
       </c>
@@ -24824,7 +24824,7 @@
       <c r="E18" s="35"/>
     </row>
     <row r="19" customFormat="false" ht="50.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="51" t="n"/>
+      <c r="A19" s="51"/>
       <c r="B19" s="57" t="s">
         <v>135</v>
       </c>
@@ -25231,7 +25231,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
@@ -25353,7 +25353,7 @@
       <c r="E9" s="31"/>
     </row>
     <row r="10" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="36" t="n"/>
+      <c r="A10" s="36"/>
       <c r="B10" s="52" t="s">
         <v>89</v>
       </c>
@@ -25375,7 +25375,7 @@
       <c r="E11" s="31"/>
     </row>
     <row r="12" customFormat="false" ht="33" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="51" t="n"/>
+      <c r="A12" s="51"/>
       <c r="B12" s="53" t="s">
         <v>123</v>
       </c>
@@ -25397,7 +25397,7 @@
       <c r="E13" s="55"/>
     </row>
     <row r="14" customFormat="false" ht="33.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="36" t="n"/>
+      <c r="A14" s="36"/>
       <c r="B14" s="57" t="s">
         <v>143</v>
       </c>
@@ -25408,7 +25408,7 @@
       <c r="E14" s="35"/>
     </row>
     <row r="15" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="36" t="n"/>
+      <c r="A15" s="36"/>
       <c r="B15" s="37" t="s">
         <v>145</v>
       </c>
@@ -25419,7 +25419,7 @@
       <c r="E15" s="35"/>
     </row>
     <row r="16" customFormat="false" ht="33" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="51" t="n"/>
+      <c r="A16" s="51"/>
       <c r="B16" s="57" t="s">
         <v>146</v>
       </c>
@@ -25833,7 +25833,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
@@ -25955,7 +25955,7 @@
       <c r="E9" s="31"/>
     </row>
     <row r="10" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="36" t="n"/>
+      <c r="A10" s="36"/>
       <c r="B10" s="52" t="s">
         <v>89</v>
       </c>
@@ -25964,7 +25964,7 @@
       <c r="E10" s="35"/>
     </row>
     <row r="11" customFormat="false" ht="50.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="51" t="n"/>
+      <c r="A11" s="51"/>
       <c r="B11" s="60" t="s">
         <v>154</v>
       </c>
@@ -25986,7 +25986,7 @@
       <c r="E12" s="71"/>
     </row>
     <row r="13" customFormat="false" ht="33.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="51" t="n"/>
+      <c r="A13" s="51"/>
       <c r="B13" s="60" t="s">
         <v>157</v>
       </c>
@@ -26008,7 +26008,7 @@
       <c r="E14" s="71"/>
     </row>
     <row r="15" s="74" customFormat="true" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="51" t="n"/>
+      <c r="A15" s="51"/>
       <c r="B15" s="53" t="s">
         <v>159</v>
       </c>
@@ -26019,7 +26019,7 @@
       <c r="E15" s="73"/>
     </row>
     <row r="16" s="74" customFormat="true" ht="82.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="51" t="n"/>
+      <c r="A16" s="51"/>
       <c r="B16" s="53" t="s">
         <v>161</v>
       </c>
@@ -26030,7 +26030,7 @@
       <c r="E16" s="73"/>
     </row>
     <row r="17" s="74" customFormat="true" ht="77.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="51" t="n"/>
+      <c r="A17" s="51"/>
       <c r="B17" s="53" t="s">
         <v>163</v>
       </c>
@@ -26041,7 +26041,7 @@
       <c r="E17" s="73"/>
     </row>
     <row r="18" customFormat="false" ht="126" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="76" t="n"/>
+      <c r="A18" s="76"/>
       <c r="B18" s="77" t="s">
         <v>165</v>
       </c>
@@ -26079,7 +26079,7 @@
       <c r="E21" s="35"/>
     </row>
     <row r="22" customFormat="false" ht="130.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="51" t="n"/>
+      <c r="A22" s="51"/>
       <c r="B22" s="53" t="s">
         <v>170</v>
       </c>
@@ -26090,7 +26090,7 @@
       <c r="E22" s="35"/>
     </row>
     <row r="23" customFormat="false" ht="24.75" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="51" t="n"/>
+      <c r="A23" s="51"/>
       <c r="B23" s="53" t="s">
         <v>172</v>
       </c>
@@ -26110,7 +26110,7 @@
       <c r="E24" s="82"/>
     </row>
     <row r="25" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="83" t="n"/>
+      <c r="A25" s="83"/>
       <c r="B25" s="84" t="s">
         <v>175</v>
       </c>
@@ -26121,7 +26121,7 @@
       </c>
     </row>
     <row r="26" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="83" t="n"/>
+      <c r="A26" s="83"/>
       <c r="B26" s="84" t="s">
         <v>175</v>
       </c>
@@ -26132,7 +26132,7 @@
       </c>
     </row>
     <row r="27" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="83" t="n"/>
+      <c r="A27" s="83"/>
       <c r="B27" s="84" t="s">
         <v>175</v>
       </c>
@@ -26143,7 +26143,7 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="83" t="n"/>
+      <c r="A28" s="83"/>
       <c r="B28" s="84" t="s">
         <v>175</v>
       </c>
@@ -26554,7 +26554,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
@@ -26676,7 +26676,7 @@
       <c r="E9" s="31"/>
     </row>
     <row r="10" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="51" t="n"/>
+      <c r="A10" s="51"/>
       <c r="B10" s="37" t="s">
         <v>89</v>
       </c>
@@ -26698,7 +26698,7 @@
       <c r="E11" s="31"/>
     </row>
     <row r="12" s="74" customFormat="true" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="51" t="n"/>
+      <c r="A12" s="51"/>
       <c r="B12" s="67" t="s">
         <v>179</v>
       </c>
@@ -26720,7 +26720,7 @@
       <c r="E13" s="87"/>
     </row>
     <row r="14" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="51" t="n"/>
+      <c r="A14" s="51"/>
       <c r="B14" s="57" t="s">
         <v>181</v>
       </c>
@@ -26731,7 +26731,7 @@
       <c r="E14" s="35"/>
     </row>
     <row r="15" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="51" t="n"/>
+      <c r="A15" s="51"/>
       <c r="B15" s="57" t="s">
         <v>183</v>
       </c>
@@ -26740,7 +26740,7 @@
       <c r="E15" s="35"/>
     </row>
     <row r="16" customFormat="false" ht="33" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="51" t="n"/>
+      <c r="A16" s="51"/>
       <c r="B16" s="57" t="s">
         <v>184</v>
       </c>
@@ -26751,7 +26751,7 @@
       <c r="E16" s="35"/>
     </row>
     <row r="17" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="51" t="n"/>
+      <c r="A17" s="51"/>
       <c r="B17" s="57" t="s">
         <v>186</v>
       </c>
@@ -26762,7 +26762,7 @@
       <c r="E17" s="35"/>
     </row>
     <row r="18" customFormat="false" ht="33.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="51" t="n"/>
+      <c r="A18" s="51"/>
       <c r="B18" s="60" t="s">
         <v>188</v>
       </c>
@@ -26773,7 +26773,7 @@
       <c r="E18" s="35"/>
     </row>
     <row r="19" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="51" t="n"/>
+      <c r="A19" s="51"/>
       <c r="B19" s="89" t="s">
         <v>190</v>
       </c>
@@ -26784,7 +26784,7 @@
       <c r="E19" s="35"/>
     </row>
     <row r="20" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="51" t="n"/>
+      <c r="A20" s="51"/>
       <c r="B20" s="90" t="s">
         <v>191</v>
       </c>
@@ -27184,7 +27184,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
@@ -27307,7 +27307,7 @@
       <c r="E9" s="55"/>
     </row>
     <row r="10" customFormat="false" ht="33.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="36" t="n"/>
+      <c r="A10" s="36"/>
       <c r="B10" s="60" t="s">
         <v>89</v>
       </c>
@@ -27318,7 +27318,7 @@
       <c r="E10" s="35"/>
     </row>
     <row r="11" customFormat="false" ht="33" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="36" t="n"/>
+      <c r="A11" s="36"/>
       <c r="B11" s="54" t="s">
         <v>195</v>
       </c>
@@ -27340,7 +27340,7 @@
       <c r="E12" s="31"/>
     </row>
     <row r="13" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="51" t="n"/>
+      <c r="A13" s="51"/>
       <c r="B13" s="57" t="s">
         <v>197</v>
       </c>
@@ -27351,7 +27351,7 @@
       <c r="E13" s="35"/>
     </row>
     <row r="14" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="51" t="n"/>
+      <c r="A14" s="51"/>
       <c r="B14" s="60" t="s">
         <v>199</v>
       </c>
@@ -27362,7 +27362,7 @@
       <c r="E14" s="35"/>
     </row>
     <row r="15" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="51" t="n"/>
+      <c r="A15" s="51"/>
       <c r="B15" s="60" t="s">
         <v>201</v>
       </c>
@@ -27373,7 +27373,7 @@
       <c r="E15" s="35"/>
     </row>
     <row r="16" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="51" t="n"/>
+      <c r="A16" s="51"/>
       <c r="B16" s="53" t="s">
         <v>203</v>
       </c>
@@ -27395,7 +27395,7 @@
       <c r="E17" s="71"/>
     </row>
     <row r="18" customFormat="false" ht="153" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="51" t="n"/>
+      <c r="A18" s="51"/>
       <c r="B18" s="57" t="s">
         <v>206</v>
       </c>
@@ -27406,7 +27406,7 @@
       <c r="E18" s="35"/>
     </row>
     <row r="19" customFormat="false" ht="65.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="51" t="n"/>
+      <c r="A19" s="51"/>
       <c r="B19" s="57" t="s">
         <v>208</v>
       </c>
@@ -27420,7 +27420,7 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="51" t="n"/>
+      <c r="A20" s="51"/>
       <c r="B20" s="57" t="s">
         <v>211</v>
       </c>
@@ -27434,7 +27434,7 @@
       <c r="F20" s="95"/>
     </row>
     <row r="21" customFormat="false" ht="144" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="51" t="n"/>
+      <c r="A21" s="51"/>
       <c r="B21" s="57" t="s">
         <v>214</v>
       </c>
@@ -27446,7 +27446,7 @@
       <c r="F21" s="95"/>
     </row>
     <row r="22" customFormat="false" ht="33" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="51" t="n"/>
+      <c r="A22" s="51"/>
       <c r="B22" s="57" t="s">
         <v>216</v>
       </c>
@@ -27457,7 +27457,7 @@
       <c r="E22" s="35"/>
     </row>
     <row r="23" customFormat="false" ht="33" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="51" t="n"/>
+      <c r="A23" s="51"/>
       <c r="B23" s="57" t="s">
         <v>218</v>
       </c>
@@ -27468,7 +27468,7 @@
       <c r="E23" s="35"/>
     </row>
     <row r="24" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="51" t="n"/>
+      <c r="A24" s="51"/>
       <c r="B24" s="57" t="s">
         <v>220</v>
       </c>
@@ -27479,7 +27479,7 @@
       <c r="E24" s="35"/>
     </row>
     <row r="25" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="51" t="n"/>
+      <c r="A25" s="51"/>
       <c r="B25" s="57" t="s">
         <v>222</v>
       </c>
@@ -27883,7 +27883,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
@@ -28005,7 +28005,7 @@
       <c r="E9" s="55"/>
     </row>
     <row r="10" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="36" t="n"/>
+      <c r="A10" s="36"/>
       <c r="B10" s="90" t="s">
         <v>89</v>
       </c>
@@ -28027,7 +28027,7 @@
       <c r="E11" s="31"/>
     </row>
     <row r="12" customFormat="false" ht="33" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="51" t="n"/>
+      <c r="A12" s="51"/>
       <c r="B12" s="57" t="s">
         <v>229</v>
       </c>
@@ -28038,7 +28038,7 @@
       <c r="E12" s="35"/>
     </row>
     <row r="13" customFormat="false" ht="42.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="51" t="n"/>
+      <c r="A13" s="51"/>
       <c r="B13" s="57" t="s">
         <v>231</v>
       </c>
@@ -28049,7 +28049,7 @@
       <c r="E13" s="35"/>
     </row>
     <row r="14" customFormat="false" ht="49.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="51" t="n"/>
+      <c r="A14" s="51"/>
       <c r="B14" s="60" t="s">
         <v>233</v>
       </c>
@@ -28060,7 +28060,7 @@
       <c r="E14" s="35"/>
     </row>
     <row r="15" customFormat="false" ht="49.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="51" t="n"/>
+      <c r="A15" s="51"/>
       <c r="B15" s="108" t="s">
         <v>235</v>
       </c>
@@ -28082,7 +28082,7 @@
       <c r="E16" s="71"/>
     </row>
     <row r="17" customFormat="false" ht="49.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="51" t="n"/>
+      <c r="A17" s="51"/>
       <c r="B17" s="57" t="s">
         <v>237</v>
       </c>
@@ -28093,7 +28093,7 @@
       <c r="E17" s="35"/>
     </row>
     <row r="18" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="51" t="n"/>
+      <c r="A18" s="51"/>
       <c r="B18" s="57" t="s">
         <v>239</v>
       </c>
@@ -28102,7 +28102,7 @@
       <c r="E18" s="35"/>
     </row>
     <row r="19" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="51" t="n"/>
+      <c r="A19" s="51"/>
       <c r="B19" s="89" t="s">
         <v>240</v>
       </c>
@@ -28113,7 +28113,7 @@
       <c r="E19" s="35"/>
     </row>
     <row r="20" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="51" t="n"/>
+      <c r="A20" s="51"/>
       <c r="B20" s="57" t="s">
         <v>242</v>
       </c>
@@ -28124,7 +28124,7 @@
       <c r="E20" s="35"/>
     </row>
     <row r="21" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="51" t="n"/>
+      <c r="A21" s="51"/>
       <c r="B21" s="89" t="s">
         <v>244</v>
       </c>
@@ -28135,7 +28135,7 @@
       <c r="E21" s="35"/>
     </row>
     <row r="22" customFormat="false" ht="33" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="51" t="n"/>
+      <c r="A22" s="51"/>
       <c r="B22" s="57" t="s">
         <v>246</v>
       </c>
@@ -28157,7 +28157,7 @@
       <c r="E23" s="109"/>
     </row>
     <row r="24" customFormat="false" ht="33" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="51" t="n"/>
+      <c r="A24" s="51"/>
       <c r="B24" s="57" t="s">
         <v>249</v>
       </c>
@@ -28558,7 +28558,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
@@ -28680,7 +28680,7 @@
       <c r="E9" s="125"/>
     </row>
     <row r="10" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="126" t="n"/>
+      <c r="A10" s="126"/>
       <c r="B10" s="127" t="s">
         <v>89</v>
       </c>
@@ -28702,7 +28702,7 @@
       <c r="E11" s="131"/>
     </row>
     <row r="12" customFormat="false" ht="33" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="130" t="n"/>
+      <c r="A12" s="130"/>
       <c r="B12" s="132" t="s">
         <v>253</v>
       </c>
@@ -28713,7 +28713,7 @@
       <c r="E12" s="133"/>
     </row>
     <row r="13" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="134" t="n"/>
+      <c r="A13" s="134"/>
       <c r="B13" s="132" t="s">
         <v>254</v>
       </c>
@@ -28724,7 +28724,7 @@
       <c r="E13" s="129"/>
     </row>
     <row r="14" customFormat="false" ht="33" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="134" t="n"/>
+      <c r="A14" s="134"/>
       <c r="B14" s="132" t="s">
         <v>256</v>
       </c>
@@ -28735,7 +28735,7 @@
       <c r="E14" s="129"/>
     </row>
     <row r="15" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="134" t="n"/>
+      <c r="A15" s="134"/>
       <c r="B15" s="136" t="s">
         <v>258</v>
       </c>
@@ -28757,7 +28757,7 @@
       <c r="E16" s="139"/>
     </row>
     <row r="17" customFormat="false" ht="33" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="138" t="n"/>
+      <c r="A17" s="138"/>
       <c r="B17" s="132" t="s">
         <v>260</v>
       </c>
@@ -28768,7 +28768,7 @@
       <c r="E17" s="129"/>
     </row>
     <row r="18" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="138" t="n"/>
+      <c r="A18" s="138"/>
       <c r="B18" s="132" t="s">
         <v>262</v>
       </c>
@@ -28779,7 +28779,7 @@
       <c r="E18" s="129"/>
     </row>
     <row r="19" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="138" t="n"/>
+      <c r="A19" s="138"/>
       <c r="B19" s="132" t="s">
         <v>264</v>
       </c>
@@ -28790,7 +28790,7 @@
       <c r="E19" s="129"/>
     </row>
     <row r="20" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="138" t="n"/>
+      <c r="A20" s="138"/>
       <c r="B20" s="132" t="s">
         <v>266</v>
       </c>
@@ -28801,7 +28801,7 @@
       <c r="E20" s="129"/>
     </row>
     <row r="21" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="138" t="n"/>
+      <c r="A21" s="138"/>
       <c r="B21" s="132" t="s">
         <v>268</v>
       </c>
@@ -28812,7 +28812,7 @@
       <c r="E21" s="129"/>
     </row>
     <row r="22" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="138" t="n"/>
+      <c r="A22" s="138"/>
       <c r="B22" s="132" t="s">
         <v>270</v>
       </c>

--- a/construction_template/data/templates_blank/self_inspection.xlsx
+++ b/construction_template/data/templates_blank/self_inspection.xlsx
@@ -297,7 +297,7 @@
     <t xml:space="preserve">QR</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
+    <t/>
   </si>
   <si>
     <t xml:space="preserve">              測量放樣施工抽查紀錄表</t>
@@ -338,7 +338,7 @@
         <family val="4"/>
         <charset val="136"/>
       </rPr>
-      <t xml:space="preserve"/>
+      <t/>
     </r>
     <r>
       <rPr>
@@ -347,7 +347,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"/>
+      <t/>
     </r>
     <r>
       <rPr>
@@ -357,7 +357,7 @@
         <family val="4"/>
         <charset val="136"/>
       </rPr>
-      <t xml:space="preserve"/>
+      <t/>
     </r>
     <r>
       <rPr>
@@ -366,7 +366,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"/>
+      <t/>
     </r>
     <r>
       <rPr>
@@ -376,7 +376,7 @@
         <family val="4"/>
         <charset val="136"/>
       </rPr>
-      <t xml:space="preserve"/>
+      <t/>
     </r>
     <r>
       <rPr>
@@ -385,7 +385,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"/>
+      <t/>
     </r>
   </si>
   <si>
@@ -1112,7 +1112,7 @@
         <family val="4"/>
         <charset val="136"/>
       </rPr>
-      <t xml:space="preserve"/>
+      <t/>
     </r>
     <r>
       <rPr>
@@ -1120,7 +1120,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"/>
+      <t/>
     </r>
     <r>
       <rPr>
@@ -1129,7 +1129,7 @@
         <family val="4"/>
         <charset val="136"/>
       </rPr>
-      <t xml:space="preserve"/>
+      <t/>
     </r>
     <r>
       <rPr>
@@ -1137,7 +1137,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"/>
+      <t/>
     </r>
     <r>
       <rPr>
@@ -1146,7 +1146,7 @@
         <family val="4"/>
         <charset val="136"/>
       </rPr>
-      <t xml:space="preserve"/>
+      <t/>
     </r>
     <r>
       <rPr>
@@ -1154,7 +1154,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"/>
+      <t/>
     </r>
   </si>
   <si>
@@ -2324,166 +2324,7 @@
     <t xml:space="preserve">拌合廠是否經本處同意使用</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"/>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t xml:space="preserve"/>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"/>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t xml:space="preserve"/>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"/>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t xml:space="preserve"/>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"/>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t xml:space="preserve"/>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"/>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t xml:space="preserve"/>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"/>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <sz val="8"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t xml:space="preserve"/>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"/>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <sz val="8"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t xml:space="preserve"/>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"/>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t xml:space="preserve"/>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"/>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"/>
-    </r>
+    <t/>
   </si>
   <si>
     <t xml:space="preserve">澆置</t>
@@ -4409,7 +4250,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve"/>
+    <t/>
   </si>
   <si>
     <t xml:space="preserve">              銑刨施工抽查紀錄表</t>
@@ -7700,7 +7541,7 @@
         <family val="4"/>
         <charset val="136"/>
       </rPr>
-      <t xml:space="preserve"/>
+      <t/>
     </r>
     <r>
       <rPr>
@@ -7709,7 +7550,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"/>
+      <t/>
     </r>
     <r>
       <rPr>
@@ -7719,7 +7560,7 @@
         <family val="4"/>
         <charset val="136"/>
       </rPr>
-      <t xml:space="preserve"/>
+      <t/>
     </r>
     <r>
       <rPr>
@@ -7728,7 +7569,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"/>
+      <t/>
     </r>
     <r>
       <rPr>
@@ -7738,7 +7579,7 @@
         <family val="4"/>
         <charset val="136"/>
       </rPr>
-      <t xml:space="preserve"/>
+      <t/>
     </r>
     <r>
       <rPr>
@@ -7747,7 +7588,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"/>
+      <t/>
     </r>
   </si>
   <si>

--- a/construction_template/data/templates_blank/self_inspection.xlsx
+++ b/construction_template/data/templates_blank/self_inspection.xlsx
@@ -330,63 +330,6 @@
       </rPr>
       <t xml:space="preserve">工程名稱:</t>
     </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t/>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t/>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t/>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t/>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t/>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t/>
-    </r>
   </si>
   <si>
     <r>
@@ -1104,57 +1047,6 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">工程名稱:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t/>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t/>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t/>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t/>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t/>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t/>
     </r>
   </si>
   <si>
@@ -7532,63 +7424,6 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">工程名稱:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t/>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t/>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t/>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t/>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t/>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t/>
     </r>
   </si>
   <si>

--- a/construction_template/data/templates_blank/self_inspection.xlsx
+++ b/construction_template/data/templates_blank/self_inspection.xlsx
@@ -156,7 +156,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">瀝青混凝土</t>
@@ -164,7 +164,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">施工抽查紀錄表</t>
@@ -306,7 +306,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="Times New Roman"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">編號</t>
@@ -325,7 +325,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">工程名稱:</t>
@@ -336,7 +336,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">分項工程名稱</t>
@@ -357,7 +357,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">檢查位置</t>
@@ -413,7 +413,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">無此檢查項目</t>
@@ -426,7 +426,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">抽查標準</t>
@@ -443,7 +443,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">定量定性</t>
@@ -462,7 +462,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">實際抽查情形
@@ -480,7 +480,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">敘述抽查值</t>
@@ -542,7 +542,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">高程</t>
@@ -561,7 +561,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">依據圖說填入</t>
@@ -602,7 +602,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">缺失複查結果</t>
@@ -622,7 +622,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">□已完成改善</t>
@@ -641,7 +641,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">檢附改善前中後照片</t>
@@ -660,7 +660,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">。</t>
@@ -674,7 +674,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">複查日期</t>
@@ -693,7 +693,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">年   月   日</t>
@@ -704,7 +704,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">複查人員職稱</t>
@@ -725,7 +725,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">簽名</t>
@@ -745,7 +745,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">備註</t>
@@ -773,7 +773,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">抽查標準及實際檢查情形應具體明確或量化尺寸。</t>
@@ -792,7 +792,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">檢查結果合格者註明「○」，不合格者註明「╳」，如無須檢查之項目則打「</t>
@@ -809,7 +809,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">」。</t>
@@ -828,7 +828,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">本表由監造工地現場人員實地檢查覆實記載簽認。</t>
@@ -839,7 +839,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">監造主管簽名</t>
@@ -860,7 +860,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">監造現場人員簽名</t>
@@ -883,7 +883,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="Times New Roman"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">編號</t>
@@ -914,7 +914,7 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">高程</t>
@@ -934,7 +934,7 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">依據圖說填入</t>
@@ -958,7 +958,7 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">坡度</t>
@@ -978,7 +978,7 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">依據圖說填入</t>
@@ -1025,7 +1025,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="Times New Roman"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">編號</t>
@@ -1043,7 +1043,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">工程名稱:</t>
@@ -1053,7 +1053,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">分項工程名稱</t>
@@ -1072,7 +1072,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">檢查位置</t>
@@ -1109,7 +1109,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">□已完成改善</t>
@@ -1126,7 +1126,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">檢附改善前中後照片</t>
@@ -1143,7 +1143,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">。</t>
@@ -1153,7 +1153,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">複查日期</t>
@@ -1170,7 +1170,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">年   月   日</t>
@@ -1180,7 +1180,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">複查人員職稱</t>
@@ -1199,7 +1199,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">簽名</t>
@@ -1221,7 +1221,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">編號</t>
@@ -1273,7 +1273,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">主鋼筋之標準彎鉤
@@ -1291,7 +1291,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">、</t>
@@ -1308,7 +1308,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">（</t>
@@ -1325,7 +1325,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">）
@@ -1343,7 +1343,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">肋筋及箍筋標準彎鉤
@@ -1361,7 +1361,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">、</t>
@@ -1378,7 +1378,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">、</t>
@@ -1409,7 +1409,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">交叉點及相疊處以直徑</t>
@@ -1426,7 +1426,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">以上之鐵絲綁紮牢固。
@@ -1444,7 +1444,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">交叉點之間距小於</t>
@@ -1461,7 +1461,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">，且確能保證鋼筋無移動變位之虞時，經得工程司核可後，可間隔綁紮。</t>
@@ -1474,7 +1474,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">除契約或圖說另有約定外，依下列約定辦理：
@@ -1492,7 +1492,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">搭接
@@ -1510,7 +1510,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">一般構造物內鋼筋長度超過</t>
@@ -1527,7 +1527,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">時，允許有一次搭接
@@ -1545,7 +1545,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">鋼筋搭接之位置應錯開，不得集中在同一斷面上。原則上相鄰兩根鋼筋搭接位置不得在同一斷面上，至少相距</t>
@@ -1562,7 +1562,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">倍直徑以上。
@@ -1580,7 +1580,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">應使搭接處之鋼筋緊貼，並用鐵絲綁緊堅固</t>
@@ -1599,7 +1599,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">銲接
@@ -1617,7 +1617,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">從事銲接工作（包括點銲）之銲接工應具有合格執照</t>
@@ -1636,7 +1636,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">續接器
@@ -1654,7 +1654,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">接合鋼筋應配合續接器之使用，其長度應先考慮接頭各部尺度後始可切斷，務使兩者能密接
@@ -1672,7 +1672,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">每一接合處必須潔凈、乾燥，排列於正確位置，接合處之緊密度均應予檢視
@@ -1690,7 +1690,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">相鄰鋼筋之續接至少須互相錯開</t>
@@ -1707,7 +1707,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">，同一斷面須留延伸之鋼筋所用續接器數量不得大於該鋼筋總量之</t>
@@ -1735,7 +1735,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">續接器應以扭力板手鎖緊，其扭力值應符合續接器產品建議值</t>
@@ -1752,7 +1752,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">請填數值</t>
@@ -1774,7 +1774,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">除契約或圖說另有約定外，依下列約定辦理：
@@ -1792,7 +1792,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">將鋼筋墊隔或固定於正確之位置
@@ -1810,7 +1810,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">暴露於室外之混凝土，距混凝土表面</t>
@@ -1827,7 +1827,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">範圍內之鋼筋墊塊必須為抗腐蝕或經防腐處理之材料
@@ -1845,7 +1845,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">水泥砂漿墊塊之強度至少須等於所澆置混凝土之強度</t>
@@ -1861,7 +1861,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">鋼筋組立抽查情形</t>
@@ -1878,7 +1878,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">檢附抽查照片</t>
@@ -1897,7 +1897,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">丈量</t>
@@ -1914,7 +1914,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">位置，長</t>
@@ -1931,7 +1931,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">，有</t>
@@ -1948,7 +1948,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">鋼筋</t>
@@ -1965,7 +1965,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">支，平均間距</t>
@@ -1982,7 +1982,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">，搭接長度</t>
@@ -1999,7 +1999,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">，保護層</t>
@@ -2024,7 +2024,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="Times New Roman"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">編號</t>
@@ -2054,7 +2054,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">木製模板應乾燥平直、無節瘤、無裂縫及其他缺點 
@@ -2072,7 +2072,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">其他依圖說規定抽查</t>
@@ -2094,7 +2094,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">許可誤差應維持於設計值</t>
@@ -2111,7 +2111,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">以內</t>
@@ -2142,7 +2142,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">編號</t>
@@ -2174,7 +2174,7 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">高程：</t>
@@ -2194,7 +2194,7 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">（依據圖說填入）</t>
@@ -2239,7 +2239,7 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">混凝土自加水攪拌開始，經過</t>
@@ -2258,7 +2258,7 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">分鐘</t>
@@ -2277,7 +2277,7 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">而仍未澆置者即不得使用。但如混凝土有添加本章之第</t>
@@ -2296,7 +2296,7 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">款</t>
@@ -2315,7 +2315,7 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">之</t>
@@ -2334,7 +2334,7 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">型緩凝劑、</t>
@@ -2353,7 +2353,7 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">型減水緩凝劑、</t>
@@ -2372,7 +2372,7 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">型高性能減水緩凝劑或第二型流動化混凝用化學摻料</t>
@@ -2391,7 +2391,7 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">塑化及緩凝劑</t>
@@ -2410,7 +2410,7 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">，而時間未超過</t>
@@ -2429,7 +2429,7 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">分鐘</t>
@@ -2448,7 +2448,7 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">者，應辦理坍度或坍流度試驗
@@ -2468,7 +2468,7 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">拌和後於澆置前之混凝土溫度不得低於</t>
@@ -2487,7 +2487,7 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">，亦不得高於</t>
@@ -2511,7 +2511,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">＊填寫本處核定</t>
@@ -2528,7 +2528,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">備查</t>
@@ -2545,7 +2545,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">施工廠商提送混凝土配比</t>
@@ -2562,7 +2562,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">坍度</t>
@@ -2579,7 +2579,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">坍度許可差
@@ -2590,7 +2590,7 @@
         <u val="single"/>
         <sz val="9"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">         </t>
@@ -2599,7 +2599,7 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -2641,7 +2641,7 @@
     <r>
       <rPr>
         <sz val="14"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">除契約或圖說另有約定外，依下列約定辦理：
@@ -2661,7 +2661,7 @@
     <r>
       <rPr>
         <sz val="14"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">、</t>
@@ -2678,7 +2678,7 @@
     <r>
       <rPr>
         <sz val="14"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">、</t>
@@ -2695,7 +2695,7 @@
     <r>
       <rPr>
         <sz val="14"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">、</t>
@@ -2712,7 +2712,7 @@
     <r>
       <rPr>
         <sz val="14"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">、</t>
@@ -2729,7 +2729,7 @@
     <r>
       <rPr>
         <sz val="14"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">、</t>
@@ -2747,7 +2747,7 @@
     <r>
       <rPr>
         <sz val="14"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">坍度許可差：
@@ -2765,7 +2765,7 @@
     <r>
       <rPr>
         <sz val="14"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">設計坍度</t>
@@ -2782,7 +2782,7 @@
     <r>
       <rPr>
         <sz val="14"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">以下時：</t>
@@ -2800,7 +2800,7 @@
     <r>
       <rPr>
         <sz val="14"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">設計坍度</t>
@@ -2817,7 +2817,7 @@
     <r>
       <rPr>
         <sz val="14"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">至</t>
@@ -2834,7 +2834,7 @@
     <r>
       <rPr>
         <sz val="14"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">時：</t>
@@ -2852,7 +2852,7 @@
     <r>
       <rPr>
         <sz val="14"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">設計坍度大於</t>
@@ -2869,7 +2869,7 @@
     <r>
       <rPr>
         <sz val="14"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">至</t>
@@ -2886,7 +2886,7 @@
     <r>
       <rPr>
         <sz val="14"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">時：</t>
@@ -2917,7 +2917,7 @@
     <r>
       <rPr>
         <sz val="8"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">預拌混凝土氯含量</t>
@@ -2954,7 +2954,7 @@
     <r>
       <rPr>
         <sz val="8"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">預力混凝土氯含量</t>
@@ -2992,7 +2992,7 @@
         <b val="true"/>
         <sz val="9"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">預拌混凝土：
@@ -3002,7 +3002,7 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">同一日澆置之混凝土，每一種配比以</t>
@@ -3021,7 +3021,7 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">每</t>
@@ -3061,7 +3061,7 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">每</t>
@@ -3091,7 +3091,7 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">澆置面積</t>
@@ -3110,7 +3110,7 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">為一批，每批至少一組強度試驗，混凝土試體至少</t>
@@ -3129,7 +3129,7 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">個為一組</t>
@@ -3148,7 +3148,7 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">天齡期至少</t>
@@ -3167,7 +3167,7 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">個，</t>
@@ -3186,7 +3186,7 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">天齡期至少</t>
@@ -3205,7 +3205,7 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">個</t>
@@ -3224,7 +3224,7 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">。若餘數超過</t>
@@ -3285,7 +3285,7 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">應增加一組試體。
@@ -3307,7 +3307,7 @@
         <b val="true"/>
         <sz val="9"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">預力混凝土：
@@ -3317,7 +3317,7 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">混凝土≦</t>
@@ -3357,7 +3357,7 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">組
@@ -3398,7 +3398,7 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">混凝土≦</t>
@@ -3438,7 +3438,7 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">組
@@ -3479,7 +3479,7 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">混凝土≦</t>
@@ -3519,7 +3519,7 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">組
@@ -3550,7 +3550,7 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">加取</t>
@@ -3569,7 +3569,7 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">組。</t>
@@ -3606,7 +3606,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">編號</t>
@@ -3626,7 +3626,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">檢查位置</t>
@@ -3645,7 +3645,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">人孔</t>
@@ -3679,7 +3679,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">檢驗報告及核備文件
@@ -3697,7 +3697,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">現場材料品名是否與檢驗報告之材料相符</t>
@@ -3719,7 +3719,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">依設計圖說
@@ -3737,7 +3737,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">人手孔：</t>
@@ -3754,7 +3754,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">、長度：</t>
@@ -3791,7 +3791,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">依核備之施工說明書
@@ -3809,7 +3809,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">人手孔：間距：</t>
@@ -3826,7 +3826,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">；孔徑：</t>
@@ -3879,7 +3879,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">長度：</t>
@@ -3889,7 +3889,7 @@
         <u val="single"/>
         <sz val="12"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">     </t>
@@ -3898,7 +3898,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">（依據圖說填入）                  </t>
@@ -3911,7 +3911,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="Times New Roman"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">編號</t>
@@ -3935,7 +3935,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">長度：</t>
@@ -3966,7 +3966,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">版樁打設深度</t>
@@ -3983,7 +3983,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">高程</t>
@@ -4000,7 +4000,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">是否符合設計圖說</t>
@@ -4016,7 +4016,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">直線偏差不得大於</t>
@@ -4038,7 +4038,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">不得大於</t>
@@ -4060,7 +4060,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">不得大於樁長</t>
@@ -4082,7 +4082,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">不得大於</t>
@@ -4107,7 +4107,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">監造主管簽名</t>
@@ -4126,7 +4126,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">監造現場人員簽名</t>
@@ -4151,7 +4151,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">編號</t>
@@ -4170,7 +4170,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">抽查標準</t>
@@ -4187,7 +4187,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">定量定性</t>
@@ -4206,7 +4206,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">實際抽查情形
@@ -4224,7 +4224,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">敘述抽查值</t>
@@ -4250,7 +4250,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">高程：</t>
@@ -4260,7 +4260,7 @@
         <u val="single"/>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">    </t>
@@ -4269,7 +4269,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">（依據圖說填入）</t>
@@ -4288,7 +4288,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">人手孔是否敲除降低至路面下</t>
@@ -4305,7 +4305,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">並以鐵板覆蓋俟澆置早強混凝土及填補</t>
@@ -4322,7 +4322,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">瀝青平整</t>
@@ -4344,7 +4344,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">銑刨機
@@ -4362,7 +4362,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">清掃機
@@ -4380,7 +4380,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">灑水設備</t>
@@ -4393,7 +4393,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">銑刨厚度</t>
@@ -4410,7 +4410,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">銑刨後高程</t>
@@ -4427,7 +4427,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">是否符合圖說</t>
@@ -4438,7 +4438,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">厚度：</t>
@@ -4448,7 +4448,7 @@
         <u val="single"/>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">       </t>
@@ -4467,7 +4467,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">（依據圖說填入），刨除厚度以平均厚度計算</t>
@@ -4480,7 +4480,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">是否銑刨至級配層或所剩</t>
@@ -4497,7 +4497,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">厚度未達</t>
@@ -4514,7 +4514,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">公分</t>
@@ -4524,7 +4524,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">備註</t>
@@ -4552,7 +4552,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">抽查標準及實際檢查情形應具體明確或量化尺寸。</t>
@@ -4571,7 +4571,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">檢查結果合格者註明「○」，不合格者註明「╳」，如無須檢查之項目則打「</t>
@@ -4588,7 +4588,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">」。</t>
@@ -4607,7 +4607,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">本表由監造工地現場人員實地檢查覆實記載簽認。</t>
@@ -4620,7 +4620,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="Times New Roman"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">編號</t>
@@ -4644,7 +4644,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">材料</t>
@@ -4661,7 +4661,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">出料單</t>
@@ -4678,7 +4678,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">規格是否符合規範</t>
@@ -4703,7 +4703,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">部瀝青鋪築機應配合</t>
@@ -4720,7 +4720,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">部鐵輪壓路機及</t>
@@ -4737,7 +4737,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">部膠輪壓路機
@@ -4755,7 +4755,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">部瀝青鋪築機配合</t>
@@ -4772,7 +4772,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">部振動壓路機及</t>
@@ -4789,7 +4789,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">部膠輪壓路機
@@ -4807,7 +4807,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">僅鋪橋面或每日鋪築量少於</t>
@@ -4824,7 +4824,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">時，僅須配備</t>
@@ -4841,7 +4841,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">部鐵輪壓路機即可
@@ -4859,7 +4859,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">厚度</t>
@@ -4876,7 +4876,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">以下之瀝青路面，不得使用振動壓路機</t>
@@ -4889,7 +4889,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">膠輪壓路機（輪胎數≧</t>
@@ -4906,7 +4906,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">）</t>
@@ -4940,7 +4940,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">舖築時溫度核對</t>
@@ -4959,7 +4959,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">舖築時溫度＜</t>
@@ -4991,7 +4991,7 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">厚度：</t>
@@ -5001,7 +5001,7 @@
         <u val="single"/>
         <sz val="9"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">     </t>
@@ -5010,7 +5010,7 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">（依據圖說填入 ）       </t>
@@ -5023,7 +5023,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">道路工程鋪面完成滾壓後以</t>
@@ -5040,7 +5040,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">直規或高低式平坦儀檢驗，</t>
@@ -5057,7 +5057,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">標準差：
@@ -5075,7 +5075,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">一般道路</t>
@@ -5092,7 +5092,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">設計速率＜</t>
@@ -5109,7 +5109,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">者</t>
@@ -5126,7 +5126,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">合格
@@ -5144,7 +5144,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">快速道路</t>
@@ -5161,7 +5161,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">設計速率≧</t>
@@ -5178,7 +5178,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">者</t>
@@ -5195,7 +5195,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">：</t>
@@ -5212,7 +5212,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">合格
@@ -5230,7 +5230,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">人手孔蓋中心點：以</t>
@@ -5247,7 +5247,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">長之直規量測，檢測值之任何一種小於</t>
@@ -5269,7 +5269,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">編號</t>
@@ -5289,7 +5289,7 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">高程：</t>
@@ -5299,7 +5299,7 @@
         <u val="single"/>
         <sz val="9"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">     </t>
@@ -5308,7 +5308,7 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">（依據圖說填入）                   </t>
@@ -5331,7 +5331,7 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">規格：</t>
@@ -5341,7 +5341,7 @@
         <u val="single"/>
         <sz val="9"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">     </t>
@@ -5350,7 +5350,7 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">（依據圖說填入）                   </t>
@@ -5411,7 +5411,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">缺失複查結果</t>
@@ -5431,7 +5431,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">□已完成改善</t>
@@ -5450,7 +5450,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">檢附改善前中後照片</t>
@@ -5469,7 +5469,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">。</t>
@@ -5480,7 +5480,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">複查日期</t>
@@ -5499,7 +5499,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">年   月   日</t>
@@ -5510,7 +5510,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">複查人員職稱</t>
@@ -5531,7 +5531,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">簽名</t>
@@ -5554,7 +5554,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">編號</t>
@@ -5574,7 +5574,7 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">高程：</t>
@@ -5584,7 +5584,7 @@
         <u val="single"/>
         <sz val="10"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">     </t>
@@ -5593,7 +5593,7 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">（依據圖說填入）                   </t>
@@ -5636,7 +5636,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="Times New Roman"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">編號</t>
@@ -5693,7 +5693,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">人行道舖面有無鬆動</t>
@@ -5710,7 +5710,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">破損</t>
@@ -5729,7 +5729,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">編號</t>
@@ -5752,7 +5752,7 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">厚度：</t>
@@ -5762,7 +5762,7 @@
         <u val="single"/>
         <sz val="10"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">       （</t>
@@ -5771,7 +5771,7 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">依據圖說填入）  </t>
@@ -5808,7 +5808,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">編號</t>
@@ -5833,7 +5833,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">塗刷表面是否清除乾淨</t>
@@ -5850,7 +5850,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">含除銹</t>
@@ -5876,7 +5876,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">採用</t>
@@ -5895,7 +5895,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">漆</t>
@@ -5914,7 +5914,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">底</t>
@@ -5933,7 +5933,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">度</t>
@@ -5943,7 +5943,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">第</t>
@@ -5952,7 +5952,7 @@
       <rPr>
         <u val="single"/>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">      </t>
@@ -5960,7 +5960,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">度底漆厚度是否符合設計</t>
@@ -5971,7 +5971,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">厚度：</t>
@@ -5981,7 +5981,7 @@
         <u val="single"/>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">      </t>
@@ -5990,7 +5990,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">（依據圖說填入）                   </t>
@@ -6000,7 +6000,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">第</t>
@@ -6009,7 +6009,7 @@
       <rPr>
         <u val="single"/>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">      </t>
@@ -6017,7 +6017,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">度面漆厚度是否符合設計</t>
@@ -6030,7 +6030,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="Times New Roman"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">編號</t>
@@ -6104,7 +6104,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="Times New Roman"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">編號</t>
@@ -6131,7 +6131,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">沿鋼筋軸向多鑿除</t>
@@ -6153,7 +6153,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">鋼筋內側約</t>
@@ -6199,7 +6199,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">編號</t>
@@ -6272,7 +6272,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">編號</t>
@@ -6294,7 +6294,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">卵石應質地堅硬，表面潔淨，</t>
@@ -6303,7 +6303,7 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">直徑</t>
@@ -6313,7 +6313,7 @@
         <u val="single"/>
         <sz val="10"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">     </t>
@@ -6322,7 +6322,7 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">（依據圖說填入）           </t>
@@ -6335,7 +6335,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">籠身規格</t>
@@ -6352,7 +6352,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">網目</t>
@@ -6369,7 +6369,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">尺寸</t>
@@ -6386,7 +6386,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">是否符合規範</t>
@@ -6396,7 +6396,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">縱向排列，編結成</t>
@@ -6413,7 +6413,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">角形孔，孔長</t>
@@ -6430,7 +6430,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">，寬</t>
@@ -6447,7 +6447,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">以下，兩根鄰近鋼線之捲接處，至少繞結</t>
@@ -6464,7 +6464,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">圈以上</t>
@@ -6478,7 +6478,7 @@
       <rPr>
         <sz val="8"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">高程：</t>
@@ -6488,7 +6488,7 @@
         <u val="single"/>
         <sz val="8"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">      </t>
@@ -6497,7 +6497,7 @@
       <rPr>
         <sz val="8"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">（依據圖說填入）                   </t>
@@ -6514,7 +6514,7 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">搭接長度：</t>
@@ -6524,7 +6524,7 @@
         <u val="single"/>
         <sz val="10"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">      </t>
@@ -6533,7 +6533,7 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">（依據圖說填入）                   </t>
@@ -6546,7 +6546,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">卵石填實及填平，孔隙斟酌填以</t>
@@ -6563,7 +6563,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">卵石</t>
@@ -6573,7 +6573,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">石籠連結綁紮是否確實</t>
@@ -6590,7 +6590,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">防脫落</t>
@@ -6609,7 +6609,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">約每隔</t>
@@ -6626,7 +6626,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">用鋼線互相固結，蛇端以兩條鋼線牢結</t>
@@ -6636,7 +6636,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">石籠安放是否確實平順</t>
@@ -6653,7 +6653,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">防變形</t>
@@ -6672,7 +6672,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">相鄰兩蛇籠頂面高度相差不得大於</t>
@@ -6691,7 +6691,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">石籠之尺寸</t>
@@ -6708,7 +6708,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">長寬高</t>
@@ -6725,7 +6725,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">是否正確</t>
@@ -6736,7 +6736,7 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">長：</t>
@@ -6746,7 +6746,7 @@
         <u val="single"/>
         <sz val="9"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">    </t>
@@ -6755,7 +6755,7 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">、寬：</t>
@@ -6765,7 +6765,7 @@
         <u val="single"/>
         <sz val="9"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">   </t>
@@ -6774,7 +6774,7 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">、
@@ -6785,7 +6785,7 @@
         <u val="single"/>
         <sz val="9"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">     </t>
@@ -6794,7 +6794,7 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">（依據圖說填入）</t>
@@ -6813,7 +6813,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">編號</t>
@@ -6856,7 +6856,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">混凝土澆置中斷料是否超過</t>
@@ -6873,7 +6873,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">分鐘</t>
@@ -6898,7 +6898,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">養護期不得少於</t>
@@ -6915,7 +6915,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">天</t>
@@ -6932,7 +6932,7 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">長度：</t>
@@ -6942,7 +6942,7 @@
         <u val="single"/>
         <sz val="10"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">      </t>
@@ -6951,7 +6951,7 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">（依據圖說填入）                   </t>
@@ -6973,7 +6973,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">編號</t>
@@ -6998,7 +6998,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">人手孔框座</t>
@@ -7015,7 +7015,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">蓋</t>
@@ -7032,7 +7032,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">是否檢驗合格</t>
@@ -7072,7 +7072,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">方形切割</t>
@@ -7089,7 +7089,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">方正切割
@@ -7107,7 +7107,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">圓形切割</t>
@@ -7124,7 +7124,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">框座半徑≦切割半徑≦框座半徑</t>
@@ -7155,7 +7155,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">方形</t>
@@ -7173,7 +7173,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">圓形</t>
@@ -7190,7 +7190,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">切割後施工深度須大於框座深度</t>
@@ -7212,7 +7212,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">深度≧</t>
@@ -7252,7 +7252,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">安全措施是否依規定圍設妥當</t>
@@ -7269,7 +7269,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">最少</t>
@@ -7286,7 +7286,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">小時</t>
@@ -7323,7 +7323,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">小時</t>
@@ -7336,7 +7336,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">編號</t>
@@ -7400,7 +7400,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">編號</t>
@@ -7420,7 +7420,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">工程名稱:</t>
@@ -7450,7 +7450,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">無此檢查項目</t>
@@ -7461,7 +7461,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">抽查標準</t>
@@ -7480,7 +7480,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">定量定性</t>
@@ -7501,7 +7501,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">實際抽查情形
@@ -7521,7 +7521,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">敘述抽查值</t>
@@ -7546,7 +7546,7 @@
         <u val="single"/>
         <sz val="11"/>
         <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">         </t>
@@ -7555,7 +7555,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">種子</t>
@@ -7570,7 +7570,7 @@
         <u val="single"/>
         <sz val="11"/>
         <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">           </t>
@@ -7579,7 +7579,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">色</t>
@@ -7599,7 +7599,7 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">出貨證明</t>
@@ -7618,7 +7618,7 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">型錄</t>
@@ -7632,7 +7632,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">□已完成改善</t>
@@ -7651,7 +7651,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">檢附改善前中後照片</t>
@@ -7670,7 +7670,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">。</t>
@@ -7681,7 +7681,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">□未完成改善</t>
@@ -7700,7 +7700,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">填具「缺失改善追蹤表」進行追蹤改善。</t>
@@ -7733,7 +7733,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">抽查標準及實際檢查情形應具體明確或量化尺寸。</t>
@@ -7754,7 +7754,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">檢查結果合格者註明「○」</t>
@@ -7773,7 +7773,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">不合格者註明「╳」</t>
@@ -7792,7 +7792,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">如無須檢查之項目則打「╱」</t>
@@ -7801,7 +7801,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">。</t>
@@ -7822,7 +7822,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">本表由監造工地人員實地檢查覆實記載簽認。</t>
@@ -7836,7 +7836,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">規格</t>
@@ -7855,7 +7855,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">盆徑</t>
@@ -7874,7 +7874,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">寸</t>
@@ -7892,7 +7892,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">監造現場人員簽名</t>
@@ -7915,7 +7915,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="Times New Roman"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">編號</t>
@@ -7978,7 +7978,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">以下僅可做為基底背填
@@ -7996,7 +7996,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">大塊石為面層</t>
@@ -8024,7 +8024,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">□已完成改善</t>
@@ -8041,7 +8041,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">檢附改善前中後照片</t>
@@ -8058,7 +8058,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">。</t>
@@ -8068,7 +8068,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">複查日期</t>
@@ -8085,7 +8085,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">年   月   日</t>
@@ -8095,7 +8095,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">複查人員職稱</t>
@@ -8114,7 +8114,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">簽名</t>
@@ -8133,7 +8133,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">監造主管簽名</t>
@@ -8152,7 +8152,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">監造現場人員簽名</t>
@@ -8174,7 +8174,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">編號</t>
@@ -8202,7 +8202,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">符合</t>
@@ -8219,7 +8219,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">規範</t>
@@ -8253,7 +8253,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="Times New Roman"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">編號</t>
@@ -8349,7 +8349,7 @@
     </font>
     <font>
       <sz val="12"/>
-      <name val="WenQuanYi Zen Hei"/>
+      <name val="標楷體"/>
       <family val="2"/>
     </font>
     <font>
@@ -8359,7 +8359,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <name val="WenQuanYi Zen Hei"/>
+      <name val="標楷體"/>
       <family val="2"/>
     </font>
     <font>
@@ -8370,13 +8370,13 @@
     </font>
     <font>
       <sz val="18"/>
-      <name val="WenQuanYi Zen Hei"/>
+      <name val="標楷體"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FFFF0000"/>
-      <name val="WenQuanYi Zen Hei"/>
+      <name val="標楷體"/>
       <family val="2"/>
     </font>
     <font>
@@ -8389,7 +8389,7 @@
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
-      <name val="WenQuanYi Zen Hei"/>
+      <name val="標楷體"/>
       <family val="2"/>
     </font>
     <font>
@@ -8407,7 +8407,7 @@
     <font>
       <sz val="10"/>
       <color rgb="FFFF0000"/>
-      <name val="WenQuanYi Zen Hei"/>
+      <name val="標楷體"/>
       <family val="2"/>
     </font>
     <font>
@@ -8419,7 +8419,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="WenQuanYi Zen Hei"/>
+      <name val="標楷體"/>
       <family val="2"/>
     </font>
     <font>
@@ -8431,7 +8431,7 @@
     <font>
       <sz val="9"/>
       <color rgb="FFFF0000"/>
-      <name val="WenQuanYi Zen Hei"/>
+      <name val="標楷體"/>
       <family val="2"/>
     </font>
     <font>
@@ -8444,7 +8444,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="WenQuanYi Zen Hei"/>
+      <name val="標楷體"/>
       <family val="2"/>
     </font>
     <font>
@@ -8464,7 +8464,7 @@
     <font>
       <sz val="8"/>
       <color rgb="FFFF0000"/>
-      <name val="WenQuanYi Zen Hei"/>
+      <name val="標楷體"/>
       <family val="2"/>
     </font>
     <font>
@@ -8485,12 +8485,12 @@
       <u val="single"/>
       <sz val="9"/>
       <color rgb="FFFF0000"/>
-      <name val="WenQuanYi Zen Hei"/>
+      <name val="標楷體"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="14"/>
-      <name val="WenQuanYi Zen Hei"/>
+      <name val="新細明體"/>
       <family val="2"/>
     </font>
     <font>
@@ -8505,7 +8505,7 @@
       <b val="true"/>
       <sz val="9"/>
       <color rgb="FFFF0000"/>
-      <name val="WenQuanYi Zen Hei"/>
+      <name val="標楷體"/>
       <family val="2"/>
     </font>
     <font>
@@ -8524,14 +8524,14 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="WenQuanYi Zen Hei"/>
+      <name val="標楷體"/>
       <family val="2"/>
     </font>
     <font>
       <u val="single"/>
       <sz val="12"/>
       <color rgb="FFFF0000"/>
-      <name val="WenQuanYi Zen Hei"/>
+      <name val="標楷體"/>
       <family val="2"/>
     </font>
     <font>
@@ -8549,14 +8549,14 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="WenQuanYi Zen Hei"/>
+      <name val="標楷體"/>
       <family val="2"/>
     </font>
     <font>
       <u val="single"/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="WenQuanYi Zen Hei"/>
+      <name val="標楷體"/>
       <family val="2"/>
     </font>
     <font>
@@ -8569,39 +8569,39 @@
     <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
-      <name val="WenQuanYi Zen Hei"/>
+      <name val="標楷體"/>
       <family val="2"/>
     </font>
     <font>
       <u val="single"/>
       <sz val="10"/>
       <color rgb="FFFF0000"/>
-      <name val="WenQuanYi Zen Hei"/>
+      <name val="標楷體"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="WenQuanYi Zen Hei"/>
+      <name val="標楷體"/>
       <family val="2"/>
     </font>
     <font>
       <u val="single"/>
       <sz val="12"/>
-      <name val="WenQuanYi Zen Hei"/>
+      <name val="標楷體"/>
       <family val="2"/>
     </font>
     <font>
       <u val="single"/>
       <sz val="8"/>
       <color rgb="FFFF0000"/>
-      <name val="WenQuanYi Zen Hei"/>
+      <name val="標楷體"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="16"/>
       <color rgb="FF000000"/>
-      <name val="WenQuanYi Zen Hei"/>
+      <name val="新細明體"/>
       <family val="2"/>
     </font>
     <font>
@@ -8635,7 +8635,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="WenQuanYi Zen Hei"/>
+      <name val="標楷體"/>
       <family val="2"/>
     </font>
     <font>
@@ -8648,14 +8648,14 @@
     <font>
       <sz val="14"/>
       <color rgb="FF000000"/>
-      <name val="WenQuanYi Zen Hei"/>
+      <name val="標楷體"/>
       <family val="2"/>
     </font>
     <font>
       <u val="single"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="WenQuanYi Zen Hei"/>
+      <name val="標楷體"/>
       <family val="2"/>
     </font>
     <font>
